--- a/Diagramas/Normalizacion base de datos/Normalizacion_Gymlocator.xlsx
+++ b/Diagramas/Normalizacion base de datos/Normalizacion_Gymlocator.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SENA\Desktop\ADSO K 3469364\Proyecto-Gym\Diagramas\Normalizacion base de datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4E771272-AF27-4247-B30A-2319252D38CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78AF71D5-4E1C-49E5-9F0F-1A9B95E3303E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1924,13 +1924,6 @@
     <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1938,20 +1931,11 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1965,9 +1949,6 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1977,17 +1958,8 @@
     <xf numFmtId="49" fontId="0" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1996,12 +1968,13 @@
     <xf numFmtId="0" fontId="0" fillId="13" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2032,14 +2005,41 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2050,8 +2050,8 @@
     <xf numFmtId="0" fontId="0" fillId="16" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2382,34 +2382,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="31"/>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
+      <c r="A1" s="49"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
+      <c r="K1" s="49"/>
+      <c r="L1" s="49"/>
+      <c r="M1" s="49"/>
     </row>
     <row r="2" spans="1:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="31"/>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
-      <c r="I2" s="31"/>
-      <c r="J2" s="31"/>
-      <c r="K2" s="31"/>
-      <c r="L2" s="31"/>
-      <c r="M2" s="31"/>
+      <c r="A2" s="49"/>
+      <c r="B2" s="49"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="49"/>
+      <c r="G2" s="49"/>
+      <c r="H2" s="49"/>
+      <c r="I2" s="49"/>
+      <c r="J2" s="49"/>
+      <c r="K2" s="49"/>
+      <c r="L2" s="49"/>
+      <c r="M2" s="49"/>
     </row>
     <row r="4" spans="1:13" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -5982,1706 +5982,1706 @@
     <row r="24" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="25" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="26" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="46" t="s">
+      <c r="B26" s="60" t="s">
         <v>233</v>
       </c>
-      <c r="C26" s="46"/>
-      <c r="D26" s="46"/>
-      <c r="E26" s="46"/>
-      <c r="F26" s="46"/>
-      <c r="G26" s="46"/>
-      <c r="H26" s="46"/>
-      <c r="K26" s="57" t="s">
+      <c r="C26" s="60"/>
+      <c r="D26" s="60"/>
+      <c r="E26" s="60"/>
+      <c r="F26" s="60"/>
+      <c r="G26" s="60"/>
+      <c r="H26" s="60"/>
+      <c r="K26" s="61" t="s">
         <v>427</v>
       </c>
-      <c r="L26" s="58"/>
-      <c r="N26" s="59" t="s">
+      <c r="L26" s="62"/>
+      <c r="N26" s="50" t="s">
         <v>353</v>
       </c>
-      <c r="O26" s="60"/>
-      <c r="Q26" s="61" t="s">
+      <c r="O26" s="51"/>
+      <c r="Q26" s="52" t="s">
         <v>278</v>
       </c>
-      <c r="R26" s="62"/>
-      <c r="T26" s="55" t="s">
+      <c r="R26" s="53"/>
+      <c r="T26" s="45" t="s">
         <v>416</v>
       </c>
-      <c r="U26" s="55"/>
+      <c r="U26" s="45"/>
     </row>
     <row r="27" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="47" t="s">
+      <c r="B27" s="40" t="s">
         <v>234</v>
       </c>
-      <c r="C27" s="47" t="s">
+      <c r="C27" s="40" t="s">
         <v>235</v>
       </c>
-      <c r="D27" s="47" t="s">
+      <c r="D27" s="40" t="s">
         <v>201</v>
       </c>
-      <c r="E27" s="47" t="s">
+      <c r="E27" s="40" t="s">
         <v>248</v>
       </c>
-      <c r="F27" s="47" t="s">
+      <c r="F27" s="40" t="s">
         <v>250</v>
       </c>
-      <c r="G27" s="47" t="s">
+      <c r="G27" s="40" t="s">
         <v>236</v>
       </c>
-      <c r="H27" s="47" t="s">
+      <c r="H27" s="40" t="s">
         <v>237</v>
       </c>
-      <c r="K27" s="47" t="s">
+      <c r="K27" s="40" t="s">
         <v>249</v>
       </c>
-      <c r="L27" s="47" t="s">
+      <c r="L27" s="40" t="s">
         <v>238</v>
       </c>
-      <c r="N27" s="39" t="s">
+      <c r="N27" s="34" t="s">
         <v>354</v>
       </c>
-      <c r="O27" s="39" t="s">
+      <c r="O27" s="34" t="s">
         <v>355</v>
       </c>
-      <c r="Q27" s="35" t="s">
+      <c r="Q27" s="32" t="s">
         <v>280</v>
       </c>
-      <c r="R27" s="35" t="s">
+      <c r="R27" s="32" t="s">
         <v>281</v>
       </c>
-      <c r="T27" s="52" t="s">
+      <c r="T27" s="43" t="s">
         <v>417</v>
       </c>
-      <c r="U27" s="52" t="s">
+      <c r="U27" s="43" t="s">
         <v>418</v>
       </c>
     </row>
     <row r="28" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="34" t="s">
+      <c r="B28" s="31" t="s">
         <v>251</v>
       </c>
-      <c r="C28" s="43" t="s">
+      <c r="C28" s="37" t="s">
         <v>161</v>
       </c>
-      <c r="D28" s="43" t="s">
+      <c r="D28" s="37" t="s">
         <v>162</v>
       </c>
-      <c r="E28" s="42" t="s">
+      <c r="E28" s="36" t="s">
         <v>239</v>
       </c>
-      <c r="F28" s="48" t="s">
+      <c r="F28" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="G28" s="48" t="s">
+      <c r="G28" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="H28" s="43" t="s">
+      <c r="H28" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="K28" s="34" t="s">
+      <c r="K28" s="31" t="s">
         <v>239</v>
       </c>
-      <c r="L28" s="34" t="s">
+      <c r="L28" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="N28" s="34" t="s">
+      <c r="N28" s="31" t="s">
         <v>251</v>
       </c>
-      <c r="O28" s="40" t="s">
+      <c r="O28" s="35" t="s">
         <v>363</v>
       </c>
-      <c r="Q28" s="35" t="s">
+      <c r="Q28" s="32" t="s">
         <v>282</v>
       </c>
-      <c r="R28" s="35" t="s">
+      <c r="R28" s="32" t="s">
         <v>283</v>
       </c>
-      <c r="T28" s="35" t="s">
+      <c r="T28" s="32" t="s">
         <v>251</v>
       </c>
-      <c r="U28" s="35" t="s">
+      <c r="U28" s="32" t="s">
         <v>346</v>
       </c>
     </row>
     <row r="29" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="34" t="s">
+      <c r="B29" s="31" t="s">
         <v>252</v>
       </c>
-      <c r="C29" s="45" t="s">
+      <c r="C29" s="39" t="s">
         <v>163</v>
       </c>
-      <c r="D29" s="45" t="s">
+      <c r="D29" s="39" t="s">
         <v>164</v>
       </c>
-      <c r="E29" s="44" t="s">
+      <c r="E29" s="38" t="s">
         <v>239</v>
       </c>
-      <c r="F29" s="49" t="s">
+      <c r="F29" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="G29" s="49" t="s">
+      <c r="G29" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="H29" s="45" t="s">
+      <c r="H29" s="39" t="s">
         <v>24</v>
       </c>
-      <c r="K29" s="34" t="s">
+      <c r="K29" s="31" t="s">
         <v>240</v>
       </c>
-      <c r="L29" s="34" t="s">
+      <c r="L29" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="N29" s="34" t="s">
+      <c r="N29" s="31" t="s">
         <v>252</v>
       </c>
-      <c r="O29" s="40" t="s">
+      <c r="O29" s="35" t="s">
         <v>364</v>
       </c>
-      <c r="Q29" s="35" t="s">
+      <c r="Q29" s="32" t="s">
         <v>284</v>
       </c>
-      <c r="R29" s="35" t="s">
+      <c r="R29" s="32" t="s">
         <v>285</v>
       </c>
-      <c r="T29" s="35" t="s">
+      <c r="T29" s="32" t="s">
         <v>251</v>
       </c>
-      <c r="U29" s="35" t="s">
+      <c r="U29" s="32" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="30" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="34" t="s">
+      <c r="B30" s="31" t="s">
         <v>253</v>
       </c>
-      <c r="C30" s="43" t="s">
+      <c r="C30" s="37" t="s">
         <v>165</v>
       </c>
-      <c r="D30" s="43" t="s">
+      <c r="D30" s="37" t="s">
         <v>166</v>
       </c>
-      <c r="E30" s="42" t="s">
+      <c r="E30" s="36" t="s">
         <v>240</v>
       </c>
-      <c r="F30" s="48" t="s">
+      <c r="F30" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="G30" s="48" t="s">
+      <c r="G30" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="H30" s="43" t="s">
+      <c r="H30" s="37" t="s">
         <v>33</v>
       </c>
-      <c r="K30" s="34" t="s">
+      <c r="K30" s="31" t="s">
         <v>241</v>
       </c>
-      <c r="L30" s="34" t="s">
+      <c r="L30" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="N30" s="34" t="s">
+      <c r="N30" s="31" t="s">
         <v>253</v>
       </c>
-      <c r="O30" s="40" t="s">
+      <c r="O30" s="35" t="s">
         <v>365</v>
       </c>
-      <c r="Q30" s="35" t="s">
+      <c r="Q30" s="32" t="s">
         <v>286</v>
       </c>
-      <c r="R30" s="35" t="s">
+      <c r="R30" s="32" t="s">
         <v>287</v>
       </c>
-      <c r="T30" s="35" t="s">
+      <c r="T30" s="32" t="s">
         <v>252</v>
       </c>
-      <c r="U30" s="35" t="s">
+      <c r="U30" s="32" t="s">
         <v>348</v>
       </c>
     </row>
     <row r="31" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="34" t="s">
+      <c r="B31" s="31" t="s">
         <v>254</v>
       </c>
-      <c r="C31" s="45" t="s">
+      <c r="C31" s="39" t="s">
         <v>167</v>
       </c>
-      <c r="D31" s="45" t="s">
+      <c r="D31" s="39" t="s">
         <v>168</v>
       </c>
-      <c r="E31" s="44" t="s">
+      <c r="E31" s="38" t="s">
         <v>239</v>
       </c>
-      <c r="F31" s="49" t="s">
+      <c r="F31" s="42" t="s">
         <v>38</v>
       </c>
-      <c r="G31" s="49" t="s">
+      <c r="G31" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="H31" s="45" t="s">
+      <c r="H31" s="39" t="s">
         <v>40</v>
       </c>
-      <c r="K31" s="34" t="s">
+      <c r="K31" s="31" t="s">
         <v>242</v>
       </c>
-      <c r="L31" s="34" t="s">
+      <c r="L31" s="31" t="s">
         <v>105</v>
       </c>
-      <c r="N31" s="34" t="s">
+      <c r="N31" s="31" t="s">
         <v>254</v>
       </c>
-      <c r="O31" s="40" t="s">
+      <c r="O31" s="35" t="s">
         <v>366</v>
       </c>
-      <c r="Q31" s="35" t="s">
+      <c r="Q31" s="32" t="s">
         <v>288</v>
       </c>
-      <c r="R31" s="35" t="s">
+      <c r="R31" s="32" t="s">
         <v>289</v>
       </c>
-      <c r="T31" s="35" t="s">
+      <c r="T31" s="32" t="s">
         <v>253</v>
       </c>
-      <c r="U31" s="35" t="s">
+      <c r="U31" s="32" t="s">
         <v>349</v>
       </c>
     </row>
     <row r="32" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="34" t="s">
+      <c r="B32" s="31" t="s">
         <v>255</v>
       </c>
-      <c r="C32" s="43" t="s">
+      <c r="C32" s="37" t="s">
         <v>169</v>
       </c>
-      <c r="D32" s="43" t="s">
+      <c r="D32" s="37" t="s">
         <v>170</v>
       </c>
-      <c r="E32" s="42" t="s">
+      <c r="E32" s="36" t="s">
         <v>239</v>
       </c>
-      <c r="F32" s="48" t="s">
+      <c r="F32" s="41" t="s">
         <v>46</v>
       </c>
-      <c r="G32" s="48" t="s">
+      <c r="G32" s="41" t="s">
         <v>47</v>
       </c>
-      <c r="H32" s="43" t="s">
+      <c r="H32" s="37" t="s">
         <v>48</v>
       </c>
-      <c r="N32" s="34" t="s">
+      <c r="N32" s="31" t="s">
         <v>255</v>
       </c>
-      <c r="O32" s="40" t="s">
+      <c r="O32" s="35" t="s">
         <v>367</v>
       </c>
-      <c r="Q32" s="35" t="s">
+      <c r="Q32" s="32" t="s">
         <v>290</v>
       </c>
-      <c r="R32" s="35" t="s">
+      <c r="R32" s="32" t="s">
         <v>291</v>
       </c>
-      <c r="T32" s="35" t="s">
+      <c r="T32" s="32" t="s">
         <v>253</v>
       </c>
-      <c r="U32" s="35" t="s">
+      <c r="U32" s="32" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="33" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="34" t="s">
+      <c r="B33" s="31" t="s">
         <v>256</v>
       </c>
-      <c r="C33" s="45" t="s">
+      <c r="C33" s="39" t="s">
         <v>171</v>
       </c>
-      <c r="D33" s="45" t="s">
+      <c r="D33" s="39" t="s">
         <v>172</v>
       </c>
-      <c r="E33" s="44" t="s">
+      <c r="E33" s="38" t="s">
         <v>241</v>
       </c>
-      <c r="F33" s="49" t="s">
+      <c r="F33" s="42" t="s">
         <v>53</v>
       </c>
-      <c r="G33" s="49" t="s">
+      <c r="G33" s="42" t="s">
         <v>54</v>
       </c>
-      <c r="H33" s="45" t="s">
+      <c r="H33" s="39" t="s">
         <v>55</v>
       </c>
-      <c r="K33" s="63" t="s">
+      <c r="K33" s="54" t="s">
         <v>414</v>
       </c>
-      <c r="L33" s="64"/>
-      <c r="N33" s="34" t="s">
+      <c r="L33" s="55"/>
+      <c r="N33" s="31" t="s">
         <v>256</v>
       </c>
-      <c r="O33" s="40" t="s">
+      <c r="O33" s="35" t="s">
         <v>368</v>
       </c>
-      <c r="Q33" s="35" t="s">
+      <c r="Q33" s="32" t="s">
         <v>292</v>
       </c>
-      <c r="R33" s="35" t="s">
+      <c r="R33" s="32" t="s">
         <v>293</v>
       </c>
-      <c r="T33" s="35" t="s">
+      <c r="T33" s="32" t="s">
         <v>254</v>
       </c>
-      <c r="U33" s="35" t="s">
+      <c r="U33" s="32" t="s">
         <v>351</v>
       </c>
     </row>
     <row r="34" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="34" t="s">
+      <c r="B34" s="31" t="s">
         <v>257</v>
       </c>
-      <c r="C34" s="43" t="s">
+      <c r="C34" s="37" t="s">
         <v>173</v>
       </c>
-      <c r="D34" s="43" t="s">
+      <c r="D34" s="37" t="s">
         <v>174</v>
       </c>
-      <c r="E34" s="42" t="s">
+      <c r="E34" s="36" t="s">
         <v>239</v>
       </c>
-      <c r="F34" s="48" t="s">
+      <c r="F34" s="41" t="s">
         <v>62</v>
       </c>
-      <c r="G34" s="48" t="s">
+      <c r="G34" s="41" t="s">
         <v>63</v>
       </c>
-      <c r="H34" s="43" t="s">
+      <c r="H34" s="37" t="s">
         <v>64</v>
       </c>
-      <c r="K34" s="52" t="s">
+      <c r="K34" s="43" t="s">
         <v>371</v>
       </c>
-      <c r="L34" s="52" t="s">
+      <c r="L34" s="43" t="s">
         <v>415</v>
       </c>
-      <c r="N34" s="34" t="s">
+      <c r="N34" s="31" t="s">
         <v>257</v>
       </c>
-      <c r="O34" s="40" t="s">
+      <c r="O34" s="35" t="s">
         <v>369</v>
       </c>
-      <c r="Q34" s="35" t="s">
+      <c r="Q34" s="32" t="s">
         <v>294</v>
       </c>
-      <c r="R34" s="35" t="s">
+      <c r="R34" s="32" t="s">
         <v>295</v>
       </c>
-      <c r="T34" s="35" t="s">
+      <c r="T34" s="32" t="s">
         <v>254</v>
       </c>
-      <c r="U34" s="35" t="s">
+      <c r="U34" s="32" t="s">
         <v>346</v>
       </c>
     </row>
     <row r="35" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="34" t="s">
+      <c r="B35" s="31" t="s">
         <v>258</v>
       </c>
-      <c r="C35" s="45" t="s">
+      <c r="C35" s="39" t="s">
         <v>175</v>
       </c>
-      <c r="D35" s="45" t="s">
+      <c r="D35" s="39" t="s">
         <v>176</v>
       </c>
-      <c r="E35" s="44" t="s">
+      <c r="E35" s="38" t="s">
         <v>239</v>
       </c>
-      <c r="F35" s="49" t="s">
+      <c r="F35" s="42" t="s">
         <v>68</v>
       </c>
-      <c r="G35" s="49" t="s">
+      <c r="G35" s="42" t="s">
         <v>69</v>
       </c>
-      <c r="H35" s="45" t="s">
+      <c r="H35" s="39" t="s">
         <v>70</v>
       </c>
-      <c r="K35" s="35" t="s">
+      <c r="K35" s="32" t="s">
         <v>394</v>
       </c>
-      <c r="L35" s="35" t="s">
+      <c r="L35" s="32" t="s">
         <v>251</v>
       </c>
-      <c r="N35" s="34" t="s">
+      <c r="N35" s="31" t="s">
         <v>258</v>
       </c>
-      <c r="O35" s="40" t="s">
+      <c r="O35" s="35" t="s">
         <v>356</v>
       </c>
-      <c r="Q35" s="35" t="s">
+      <c r="Q35" s="32" t="s">
         <v>296</v>
       </c>
-      <c r="R35" s="35" t="s">
+      <c r="R35" s="32" t="s">
         <v>297</v>
       </c>
-      <c r="T35" s="35" t="s">
+      <c r="T35" s="32" t="s">
         <v>255</v>
       </c>
-      <c r="U35" s="35" t="s">
+      <c r="U35" s="32" t="s">
         <v>352</v>
       </c>
     </row>
     <row r="36" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="34" t="s">
+      <c r="B36" s="31" t="s">
         <v>259</v>
       </c>
-      <c r="C36" s="43" t="s">
+      <c r="C36" s="37" t="s">
         <v>177</v>
       </c>
-      <c r="D36" s="43" t="s">
+      <c r="D36" s="37" t="s">
         <v>178</v>
       </c>
-      <c r="E36" s="42" t="s">
+      <c r="E36" s="36" t="s">
         <v>240</v>
       </c>
-      <c r="F36" s="48" t="s">
+      <c r="F36" s="41" t="s">
         <v>73</v>
       </c>
-      <c r="G36" s="48" t="s">
+      <c r="G36" s="41" t="s">
         <v>74</v>
       </c>
-      <c r="H36" s="43" t="s">
+      <c r="H36" s="37" t="s">
         <v>75</v>
       </c>
-      <c r="K36" s="35" t="s">
+      <c r="K36" s="32" t="s">
         <v>394</v>
       </c>
-      <c r="L36" s="35" t="s">
+      <c r="L36" s="32" t="s">
         <v>252</v>
       </c>
-      <c r="N36" s="34" t="s">
+      <c r="N36" s="31" t="s">
         <v>259</v>
       </c>
-      <c r="O36" s="40" t="s">
+      <c r="O36" s="35" t="s">
         <v>357</v>
       </c>
-      <c r="Q36" s="35" t="s">
+      <c r="Q36" s="32" t="s">
         <v>298</v>
       </c>
-      <c r="R36" s="35" t="s">
+      <c r="R36" s="32" t="s">
         <v>299</v>
       </c>
-      <c r="T36" s="35" t="s">
+      <c r="T36" s="32" t="s">
         <v>256</v>
       </c>
-      <c r="U36" s="35" t="s">
+      <c r="U36" s="32" t="s">
         <v>348</v>
       </c>
     </row>
     <row r="37" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="34" t="s">
+      <c r="B37" s="31" t="s">
         <v>260</v>
       </c>
-      <c r="C37" s="45" t="s">
+      <c r="C37" s="39" t="s">
         <v>179</v>
       </c>
-      <c r="D37" s="45" t="s">
+      <c r="D37" s="39" t="s">
         <v>180</v>
       </c>
-      <c r="E37" s="44" t="s">
+      <c r="E37" s="38" t="s">
         <v>239</v>
       </c>
-      <c r="F37" s="49" t="s">
+      <c r="F37" s="42" t="s">
         <v>79</v>
       </c>
-      <c r="G37" s="49" t="s">
+      <c r="G37" s="42" t="s">
         <v>80</v>
       </c>
-      <c r="H37" s="45" t="s">
+      <c r="H37" s="39" t="s">
         <v>81</v>
       </c>
-      <c r="K37" s="35" t="s">
+      <c r="K37" s="32" t="s">
         <v>395</v>
       </c>
-      <c r="L37" s="35" t="s">
+      <c r="L37" s="32" t="s">
         <v>253</v>
       </c>
-      <c r="N37" s="34" t="s">
+      <c r="N37" s="31" t="s">
         <v>260</v>
       </c>
-      <c r="O37" s="40" t="s">
+      <c r="O37" s="35" t="s">
         <v>358</v>
       </c>
-      <c r="Q37" s="35" t="s">
+      <c r="Q37" s="32" t="s">
         <v>300</v>
       </c>
-      <c r="R37" s="35" t="s">
+      <c r="R37" s="32" t="s">
         <v>301</v>
       </c>
-      <c r="T37" s="35" t="s">
+      <c r="T37" s="32" t="s">
         <v>256</v>
       </c>
-      <c r="U37" s="35" t="s">
+      <c r="U37" s="32" t="s">
         <v>346</v>
       </c>
     </row>
     <row r="38" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="34" t="s">
+      <c r="B38" s="31" t="s">
         <v>261</v>
       </c>
-      <c r="C38" s="43" t="s">
+      <c r="C38" s="37" t="s">
         <v>181</v>
       </c>
-      <c r="D38" s="43" t="s">
+      <c r="D38" s="37" t="s">
         <v>182</v>
       </c>
-      <c r="E38" s="42" t="s">
+      <c r="E38" s="36" t="s">
         <v>239</v>
       </c>
-      <c r="F38" s="48" t="s">
+      <c r="F38" s="41" t="s">
         <v>85</v>
       </c>
-      <c r="G38" s="48" t="s">
+      <c r="G38" s="41" t="s">
         <v>86</v>
       </c>
-      <c r="H38" s="43" t="s">
+      <c r="H38" s="37" t="s">
         <v>87</v>
       </c>
-      <c r="K38" s="35" t="s">
+      <c r="K38" s="32" t="s">
         <v>396</v>
       </c>
-      <c r="L38" s="35" t="s">
+      <c r="L38" s="32" t="s">
         <v>254</v>
       </c>
-      <c r="N38" s="34" t="s">
+      <c r="N38" s="31" t="s">
         <v>261</v>
       </c>
-      <c r="O38" s="40" t="s">
+      <c r="O38" s="35" t="s">
         <v>359</v>
       </c>
-      <c r="Q38" s="35" t="s">
+      <c r="Q38" s="32" t="s">
         <v>302</v>
       </c>
-      <c r="R38" s="35" t="s">
+      <c r="R38" s="32" t="s">
         <v>303</v>
       </c>
-      <c r="T38" s="35" t="s">
+      <c r="T38" s="32" t="s">
         <v>257</v>
       </c>
-      <c r="U38" s="35" t="s">
+      <c r="U38" s="32" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="39" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="34" t="s">
+      <c r="B39" s="31" t="s">
         <v>262</v>
       </c>
-      <c r="C39" s="45" t="s">
+      <c r="C39" s="39" t="s">
         <v>183</v>
       </c>
-      <c r="D39" s="45" t="s">
+      <c r="D39" s="39" t="s">
         <v>184</v>
       </c>
-      <c r="E39" s="44" t="s">
+      <c r="E39" s="38" t="s">
         <v>241</v>
       </c>
-      <c r="F39" s="49" t="s">
+      <c r="F39" s="42" t="s">
         <v>91</v>
       </c>
-      <c r="G39" s="49" t="s">
+      <c r="G39" s="42" t="s">
         <v>92</v>
       </c>
-      <c r="H39" s="45" t="s">
+      <c r="H39" s="39" t="s">
         <v>93</v>
       </c>
-      <c r="K39" s="35" t="s">
+      <c r="K39" s="32" t="s">
         <v>397</v>
       </c>
-      <c r="L39" s="35" t="s">
+      <c r="L39" s="32" t="s">
         <v>256</v>
       </c>
-      <c r="N39" s="34" t="s">
+      <c r="N39" s="31" t="s">
         <v>262</v>
       </c>
-      <c r="O39" s="40" t="s">
+      <c r="O39" s="35" t="s">
         <v>360</v>
       </c>
-      <c r="Q39" s="35" t="s">
+      <c r="Q39" s="32" t="s">
         <v>304</v>
       </c>
-      <c r="R39" s="35" t="s">
+      <c r="R39" s="32" t="s">
         <v>305</v>
       </c>
-      <c r="T39" s="35" t="s">
+      <c r="T39" s="32" t="s">
         <v>257</v>
       </c>
-      <c r="U39" s="35" t="s">
+      <c r="U39" s="32" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="40" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="34" t="s">
+      <c r="B40" s="31" t="s">
         <v>263</v>
       </c>
-      <c r="C40" s="43" t="s">
+      <c r="C40" s="37" t="s">
         <v>185</v>
       </c>
-      <c r="D40" s="43" t="s">
+      <c r="D40" s="37" t="s">
         <v>186</v>
       </c>
-      <c r="E40" s="42" t="s">
+      <c r="E40" s="36" t="s">
         <v>239</v>
       </c>
-      <c r="F40" s="48" t="s">
+      <c r="F40" s="41" t="s">
         <v>95</v>
       </c>
-      <c r="G40" s="48" t="s">
+      <c r="G40" s="41" t="s">
         <v>96</v>
       </c>
-      <c r="H40" s="43" t="s">
+      <c r="H40" s="37" t="s">
         <v>97</v>
       </c>
-      <c r="K40" s="35" t="s">
+      <c r="K40" s="32" t="s">
         <v>397</v>
       </c>
-      <c r="L40" s="35" t="s">
+      <c r="L40" s="32" t="s">
         <v>258</v>
       </c>
-      <c r="N40" s="34" t="s">
+      <c r="N40" s="31" t="s">
         <v>263</v>
       </c>
-      <c r="O40" s="40" t="s">
+      <c r="O40" s="35" t="s">
         <v>361</v>
       </c>
-      <c r="Q40" s="35" t="s">
+      <c r="Q40" s="32" t="s">
         <v>306</v>
       </c>
-      <c r="R40" s="35" t="s">
+      <c r="R40" s="32" t="s">
         <v>307</v>
       </c>
-      <c r="T40" s="35" t="s">
+      <c r="T40" s="32" t="s">
         <v>258</v>
       </c>
-      <c r="U40" s="35" t="s">
+      <c r="U40" s="32" t="s">
         <v>349</v>
       </c>
     </row>
     <row r="41" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="34" t="s">
+      <c r="B41" s="31" t="s">
         <v>264</v>
       </c>
-      <c r="C41" s="45" t="s">
+      <c r="C41" s="39" t="s">
         <v>187</v>
       </c>
-      <c r="D41" s="45" t="s">
+      <c r="D41" s="39" t="s">
         <v>188</v>
       </c>
-      <c r="E41" s="44" t="s">
+      <c r="E41" s="38" t="s">
         <v>239</v>
       </c>
-      <c r="F41" s="49" t="s">
+      <c r="F41" s="42" t="s">
         <v>101</v>
       </c>
-      <c r="G41" s="49" t="s">
+      <c r="G41" s="42" t="s">
         <v>102</v>
       </c>
-      <c r="H41" s="45" t="s">
+      <c r="H41" s="39" t="s">
         <v>103</v>
       </c>
-      <c r="K41" s="35" t="s">
+      <c r="K41" s="32" t="s">
         <v>398</v>
       </c>
-      <c r="L41" s="35" t="s">
+      <c r="L41" s="32" t="s">
         <v>257</v>
       </c>
-      <c r="N41" s="34" t="s">
+      <c r="N41" s="31" t="s">
         <v>264</v>
       </c>
-      <c r="O41" s="40" t="s">
+      <c r="O41" s="35" t="s">
         <v>362</v>
       </c>
-      <c r="Q41" s="35" t="s">
+      <c r="Q41" s="32" t="s">
         <v>308</v>
       </c>
-      <c r="R41" s="35" t="s">
+      <c r="R41" s="32" t="s">
         <v>309</v>
       </c>
-      <c r="T41" s="35" t="s">
+      <c r="T41" s="32" t="s">
         <v>259</v>
       </c>
-      <c r="U41" s="35" t="s">
+      <c r="U41" s="32" t="s">
         <v>351</v>
       </c>
     </row>
     <row r="42" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="34" t="s">
+      <c r="B42" s="31" t="s">
         <v>265</v>
       </c>
-      <c r="C42" s="43" t="s">
+      <c r="C42" s="37" t="s">
         <v>189</v>
       </c>
-      <c r="D42" s="43" t="s">
+      <c r="D42" s="37" t="s">
         <v>190</v>
       </c>
-      <c r="E42" s="42" t="s">
+      <c r="E42" s="36" t="s">
         <v>242</v>
       </c>
-      <c r="F42" s="48" t="s">
+      <c r="F42" s="41" t="s">
         <v>106</v>
       </c>
-      <c r="G42" s="48" t="s">
+      <c r="G42" s="41" t="s">
         <v>107</v>
       </c>
-      <c r="H42" s="43" t="s">
+      <c r="H42" s="37" t="s">
         <v>108</v>
       </c>
-      <c r="K42" s="35" t="s">
+      <c r="K42" s="32" t="s">
         <v>399</v>
       </c>
-      <c r="L42" s="35" t="s">
+      <c r="L42" s="32" t="s">
         <v>260</v>
       </c>
-      <c r="Q42" s="35" t="s">
+      <c r="Q42" s="32" t="s">
         <v>310</v>
       </c>
-      <c r="R42" s="35" t="s">
+      <c r="R42" s="32" t="s">
         <v>311</v>
       </c>
-      <c r="T42" s="35" t="s">
+      <c r="T42" s="32" t="s">
         <v>259</v>
       </c>
-      <c r="U42" s="35" t="s">
+      <c r="U42" s="32" t="s">
         <v>352</v>
       </c>
     </row>
     <row r="43" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="34" t="s">
+      <c r="B43" s="31" t="s">
         <v>266</v>
       </c>
-      <c r="C43" s="45" t="s">
+      <c r="C43" s="39" t="s">
         <v>191</v>
       </c>
-      <c r="D43" s="45" t="s">
+      <c r="D43" s="39" t="s">
         <v>192</v>
       </c>
-      <c r="E43" s="44" t="s">
+      <c r="E43" s="38" t="s">
         <v>239</v>
       </c>
-      <c r="F43" s="49" t="s">
+      <c r="F43" s="42" t="s">
         <v>112</v>
       </c>
-      <c r="G43" s="49" t="s">
+      <c r="G43" s="42" t="s">
         <v>113</v>
       </c>
-      <c r="H43" s="45" t="s">
+      <c r="H43" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="K43" s="35" t="s">
+      <c r="K43" s="32" t="s">
         <v>399</v>
       </c>
-      <c r="L43" s="35" t="s">
+      <c r="L43" s="32" t="s">
         <v>251</v>
       </c>
-      <c r="N43" s="65" t="s">
+      <c r="N43" s="56" t="s">
         <v>275</v>
       </c>
-      <c r="O43" s="66"/>
-      <c r="Q43" s="35" t="s">
+      <c r="O43" s="57"/>
+      <c r="Q43" s="32" t="s">
         <v>312</v>
       </c>
-      <c r="R43" s="35" t="s">
+      <c r="R43" s="32" t="s">
         <v>313</v>
       </c>
-      <c r="T43" s="35" t="s">
+      <c r="T43" s="32" t="s">
         <v>260</v>
       </c>
-      <c r="U43" s="35" t="s">
+      <c r="U43" s="32" t="s">
         <v>346</v>
       </c>
     </row>
     <row r="44" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="34" t="s">
+      <c r="B44" s="31" t="s">
         <v>267</v>
       </c>
-      <c r="C44" s="43" t="s">
+      <c r="C44" s="37" t="s">
         <v>193</v>
       </c>
-      <c r="D44" s="43" t="s">
+      <c r="D44" s="37" t="s">
         <v>194</v>
       </c>
-      <c r="E44" s="42" t="s">
+      <c r="E44" s="36" t="s">
         <v>239</v>
       </c>
-      <c r="F44" s="48" t="s">
+      <c r="F44" s="41" t="s">
         <v>118</v>
       </c>
-      <c r="G44" s="48" t="s">
+      <c r="G44" s="41" t="s">
         <v>119</v>
       </c>
-      <c r="H44" s="43" t="s">
+      <c r="H44" s="37" t="s">
         <v>120</v>
       </c>
-      <c r="K44" s="35" t="s">
+      <c r="K44" s="32" t="s">
         <v>400</v>
       </c>
-      <c r="L44" s="35" t="s">
+      <c r="L44" s="32" t="s">
         <v>255</v>
       </c>
-      <c r="N44" s="34" t="s">
+      <c r="N44" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="O44" s="34" t="s">
+      <c r="O44" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="Q44" s="35" t="s">
+      <c r="Q44" s="32" t="s">
         <v>314</v>
       </c>
-      <c r="R44" s="35" t="s">
+      <c r="R44" s="32" t="s">
         <v>315</v>
       </c>
-      <c r="T44" s="35" t="s">
+      <c r="T44" s="32" t="s">
         <v>261</v>
       </c>
-      <c r="U44" s="35" t="s">
+      <c r="U44" s="32" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="45" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="34" t="s">
+      <c r="B45" s="31" t="s">
         <v>268</v>
       </c>
-      <c r="C45" s="45" t="s">
+      <c r="C45" s="39" t="s">
         <v>195</v>
       </c>
-      <c r="D45" s="45" t="s">
+      <c r="D45" s="39" t="s">
         <v>196</v>
       </c>
-      <c r="E45" s="44" t="s">
+      <c r="E45" s="38" t="s">
         <v>239</v>
       </c>
-      <c r="F45" s="49" t="s">
+      <c r="F45" s="42" t="s">
         <v>124</v>
       </c>
-      <c r="G45" s="49" t="s">
+      <c r="G45" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="H45" s="45" t="s">
+      <c r="H45" s="39" t="s">
         <v>125</v>
       </c>
-      <c r="K45" s="35" t="s">
+      <c r="K45" s="32" t="s">
         <v>400</v>
       </c>
-      <c r="L45" s="35" t="s">
+      <c r="L45" s="32" t="s">
         <v>252</v>
       </c>
-      <c r="N45" s="35" t="s">
+      <c r="N45" s="32" t="s">
         <v>373</v>
       </c>
-      <c r="O45" s="36" t="s">
+      <c r="O45" s="33" t="s">
         <v>322</v>
       </c>
-      <c r="Q45" s="35" t="s">
+      <c r="Q45" s="32" t="s">
         <v>316</v>
       </c>
-      <c r="R45" s="35" t="s">
+      <c r="R45" s="32" t="s">
         <v>317</v>
       </c>
-      <c r="T45" s="35" t="s">
+      <c r="T45" s="32" t="s">
         <v>261</v>
       </c>
-      <c r="U45" s="35" t="s">
+      <c r="U45" s="32" t="s">
         <v>348</v>
       </c>
     </row>
     <row r="46" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="34" t="s">
+      <c r="B46" s="31" t="s">
         <v>269</v>
       </c>
-      <c r="C46" s="43" t="s">
+      <c r="C46" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="D46" s="43" t="s">
+      <c r="D46" s="37" t="s">
         <v>198</v>
       </c>
-      <c r="E46" s="42" t="s">
+      <c r="E46" s="36" t="s">
         <v>240</v>
       </c>
-      <c r="F46" s="48" t="s">
+      <c r="F46" s="41" t="s">
         <v>129</v>
       </c>
-      <c r="G46" s="48" t="s">
+      <c r="G46" s="41" t="s">
         <v>130</v>
       </c>
-      <c r="H46" s="43" t="s">
+      <c r="H46" s="37" t="s">
         <v>131</v>
       </c>
-      <c r="K46" s="35" t="s">
+      <c r="K46" s="32" t="s">
         <v>401</v>
       </c>
-      <c r="L46" s="35" t="s">
+      <c r="L46" s="32" t="s">
         <v>254</v>
       </c>
-      <c r="N46" s="35" t="s">
+      <c r="N46" s="32" t="s">
         <v>374</v>
       </c>
-      <c r="O46" s="36" t="s">
+      <c r="O46" s="33" t="s">
         <v>323</v>
       </c>
-      <c r="Q46" s="35" t="s">
+      <c r="Q46" s="32" t="s">
         <v>318</v>
       </c>
-      <c r="R46" s="35" t="s">
+      <c r="R46" s="32" t="s">
         <v>319</v>
       </c>
-      <c r="T46" s="35" t="s">
+      <c r="T46" s="32" t="s">
         <v>262</v>
       </c>
-      <c r="U46" s="35" t="s">
+      <c r="U46" s="32" t="s">
         <v>349</v>
       </c>
     </row>
     <row r="47" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="34" t="s">
+      <c r="B47" s="31" t="s">
         <v>270</v>
       </c>
-      <c r="C47" s="45" t="s">
+      <c r="C47" s="39" t="s">
         <v>199</v>
       </c>
-      <c r="D47" s="45" t="s">
+      <c r="D47" s="39" t="s">
         <v>200</v>
       </c>
-      <c r="E47" s="44" t="s">
+      <c r="E47" s="38" t="s">
         <v>239</v>
       </c>
-      <c r="F47" s="49" t="s">
+      <c r="F47" s="42" t="s">
         <v>135</v>
       </c>
-      <c r="G47" s="49" t="s">
+      <c r="G47" s="42" t="s">
         <v>136</v>
       </c>
-      <c r="H47" s="45" t="s">
+      <c r="H47" s="39" t="s">
         <v>137</v>
       </c>
-      <c r="K47" s="35" t="s">
+      <c r="K47" s="32" t="s">
         <v>402</v>
       </c>
-      <c r="L47" s="35" t="s">
+      <c r="L47" s="32" t="s">
         <v>256</v>
       </c>
-      <c r="N47" s="35" t="s">
+      <c r="N47" s="32" t="s">
         <v>375</v>
       </c>
-      <c r="O47" s="36" t="s">
+      <c r="O47" s="33" t="s">
         <v>324</v>
       </c>
-      <c r="T47" s="35" t="s">
+      <c r="T47" s="32" t="s">
         <v>262</v>
       </c>
-      <c r="U47" s="35" t="s">
+      <c r="U47" s="32" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="48" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K48" s="35" t="s">
+      <c r="K48" s="32" t="s">
         <v>402</v>
       </c>
-      <c r="L48" s="35" t="s">
+      <c r="L48" s="32" t="s">
         <v>257</v>
       </c>
-      <c r="N48" s="35" t="s">
+      <c r="N48" s="32" t="s">
         <v>376</v>
       </c>
-      <c r="O48" s="36" t="s">
+      <c r="O48" s="33" t="s">
         <v>325</v>
       </c>
-      <c r="Q48" s="67" t="s">
+      <c r="Q48" s="58" t="s">
         <v>343</v>
       </c>
-      <c r="R48" s="68"/>
-      <c r="T48" s="35" t="s">
+      <c r="R48" s="59"/>
+      <c r="T48" s="32" t="s">
         <v>263</v>
       </c>
-      <c r="U48" s="35" t="s">
+      <c r="U48" s="32" t="s">
         <v>352</v>
       </c>
     </row>
     <row r="49" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K49" s="35" t="s">
+      <c r="K49" s="32" t="s">
         <v>403</v>
       </c>
-      <c r="L49" s="35" t="s">
+      <c r="L49" s="32" t="s">
         <v>258</v>
       </c>
-      <c r="N49" s="35" t="s">
+      <c r="N49" s="32" t="s">
         <v>377</v>
       </c>
-      <c r="O49" s="36" t="s">
+      <c r="O49" s="33" t="s">
         <v>326</v>
       </c>
-      <c r="Q49" s="34" t="s">
+      <c r="Q49" s="31" t="s">
         <v>344</v>
       </c>
-      <c r="R49" s="34" t="s">
+      <c r="R49" s="31" t="s">
         <v>345</v>
       </c>
-      <c r="T49" s="35" t="s">
+      <c r="T49" s="32" t="s">
         <v>263</v>
       </c>
-      <c r="U49" s="35" t="s">
+      <c r="U49" s="32" t="s">
         <v>351</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K50" s="35" t="s">
+      <c r="K50" s="32" t="s">
         <v>404</v>
       </c>
-      <c r="L50" s="35" t="s">
+      <c r="L50" s="32" t="s">
         <v>252</v>
       </c>
-      <c r="N50" s="35" t="s">
+      <c r="N50" s="32" t="s">
         <v>378</v>
       </c>
-      <c r="O50" s="36" t="s">
+      <c r="O50" s="33" t="s">
         <v>327</v>
       </c>
-      <c r="Q50" s="34" t="s">
+      <c r="Q50" s="31" t="s">
         <v>346</v>
       </c>
-      <c r="R50" s="40" t="s">
+      <c r="R50" s="35" t="s">
         <v>82</v>
       </c>
-      <c r="T50" s="35" t="s">
+      <c r="T50" s="32" t="s">
         <v>264</v>
       </c>
-      <c r="U50" s="35" t="s">
+      <c r="U50" s="32" t="s">
         <v>348</v>
       </c>
     </row>
     <row r="51" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K51" s="35" t="s">
+      <c r="K51" s="32" t="s">
         <v>404</v>
       </c>
-      <c r="L51" s="35" t="s">
+      <c r="L51" s="32" t="s">
         <v>253</v>
       </c>
-      <c r="N51" s="35" t="s">
+      <c r="N51" s="32" t="s">
         <v>379</v>
       </c>
-      <c r="O51" s="36" t="s">
+      <c r="O51" s="33" t="s">
         <v>328</v>
       </c>
-      <c r="Q51" s="34" t="s">
+      <c r="Q51" s="31" t="s">
         <v>347</v>
       </c>
-      <c r="R51" s="40" t="s">
+      <c r="R51" s="35" t="s">
         <v>211</v>
       </c>
-      <c r="T51" s="35" t="s">
+      <c r="T51" s="32" t="s">
         <v>264</v>
       </c>
-      <c r="U51" s="35" t="s">
+      <c r="U51" s="32" t="s">
         <v>346</v>
       </c>
     </row>
     <row r="52" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="56" t="s">
+      <c r="B52" s="46" t="s">
         <v>370</v>
       </c>
-      <c r="C52" s="56"/>
-      <c r="D52" s="56"/>
-      <c r="E52" s="56"/>
-      <c r="G52" s="54" t="s">
+      <c r="C52" s="46"/>
+      <c r="D52" s="46"/>
+      <c r="E52" s="46"/>
+      <c r="G52" s="44" t="s">
         <v>271</v>
       </c>
-      <c r="H52" s="54"/>
-      <c r="I52" s="54"/>
-      <c r="K52" s="35" t="s">
+      <c r="H52" s="44"/>
+      <c r="I52" s="44"/>
+      <c r="K52" s="32" t="s">
         <v>405</v>
       </c>
-      <c r="L52" s="35" t="s">
+      <c r="L52" s="32" t="s">
         <v>254</v>
       </c>
-      <c r="N52" s="35" t="s">
+      <c r="N52" s="32" t="s">
         <v>380</v>
       </c>
-      <c r="O52" s="36" t="s">
+      <c r="O52" s="33" t="s">
         <v>329</v>
       </c>
-      <c r="Q52" s="34" t="s">
+      <c r="Q52" s="31" t="s">
         <v>348</v>
       </c>
-      <c r="R52" s="40" t="s">
+      <c r="R52" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="T52" s="35" t="s">
+      <c r="T52" s="32" t="s">
         <v>265</v>
       </c>
-      <c r="U52" s="35" t="s">
+      <c r="U52" s="32" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="53" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="34" t="s">
+      <c r="B53" s="31" t="s">
         <v>371</v>
       </c>
-      <c r="C53" s="34" t="s">
+      <c r="C53" s="31" t="s">
         <v>234</v>
       </c>
-      <c r="D53" s="34" t="s">
+      <c r="D53" s="31" t="s">
         <v>372</v>
       </c>
-      <c r="E53" s="34" t="s">
+      <c r="E53" s="31" t="s">
         <v>393</v>
       </c>
-      <c r="G53" s="34" t="s">
+      <c r="G53" s="31" t="s">
         <v>272</v>
       </c>
-      <c r="H53" s="34" t="s">
+      <c r="H53" s="31" t="s">
         <v>273</v>
       </c>
-      <c r="I53" s="34" t="s">
+      <c r="I53" s="31" t="s">
         <v>274</v>
       </c>
-      <c r="K53" s="35" t="s">
+      <c r="K53" s="32" t="s">
         <v>406</v>
       </c>
-      <c r="L53" s="35" t="s">
+      <c r="L53" s="32" t="s">
         <v>257</v>
       </c>
-      <c r="N53" s="35" t="s">
+      <c r="N53" s="32" t="s">
         <v>381</v>
       </c>
-      <c r="O53" s="36" t="s">
+      <c r="O53" s="33" t="s">
         <v>330</v>
       </c>
-      <c r="Q53" s="34" t="s">
+      <c r="Q53" s="31" t="s">
         <v>349</v>
       </c>
-      <c r="R53" s="40" t="s">
+      <c r="R53" s="35" t="s">
         <v>71</v>
       </c>
-      <c r="T53" s="35" t="s">
+      <c r="T53" s="32" t="s">
         <v>266</v>
       </c>
-      <c r="U53" s="35" t="s">
+      <c r="U53" s="32" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="54" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="34" t="s">
+      <c r="B54" s="31" t="s">
         <v>394</v>
       </c>
-      <c r="C54" s="34" t="s">
+      <c r="C54" s="31" t="s">
         <v>251</v>
       </c>
-      <c r="D54" s="42" t="s">
+      <c r="D54" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="E54" s="35" t="s">
+      <c r="E54" s="32" t="s">
         <v>373</v>
       </c>
-      <c r="G54" s="42" t="s">
+      <c r="G54" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="H54" s="43" t="s">
+      <c r="H54" s="37" t="s">
         <v>165</v>
       </c>
-      <c r="I54" s="43" t="s">
+      <c r="I54" s="37" t="s">
         <v>168</v>
       </c>
-      <c r="K54" s="35" t="s">
+      <c r="K54" s="32" t="s">
         <v>406</v>
       </c>
-      <c r="L54" s="35" t="s">
+      <c r="L54" s="32" t="s">
         <v>256</v>
       </c>
-      <c r="N54" s="35" t="s">
+      <c r="N54" s="32" t="s">
         <v>382</v>
       </c>
-      <c r="O54" s="36" t="s">
+      <c r="O54" s="33" t="s">
         <v>331</v>
       </c>
-      <c r="Q54" s="34" t="s">
+      <c r="Q54" s="31" t="s">
         <v>350</v>
       </c>
-      <c r="R54" s="40" t="s">
+      <c r="R54" s="35" t="s">
         <v>109</v>
       </c>
-      <c r="T54" s="35" t="s">
+      <c r="T54" s="32" t="s">
         <v>266</v>
       </c>
-      <c r="U54" s="35" t="s">
+      <c r="U54" s="32" t="s">
         <v>349</v>
       </c>
     </row>
     <row r="55" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="34" t="s">
+      <c r="B55" s="31" t="s">
         <v>395</v>
       </c>
-      <c r="C55" s="34" t="s">
+      <c r="C55" s="31" t="s">
         <v>252</v>
       </c>
-      <c r="D55" s="44" t="s">
+      <c r="D55" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="E55" s="35" t="s">
+      <c r="E55" s="32" t="s">
         <v>374</v>
       </c>
-      <c r="G55" s="44" t="s">
+      <c r="G55" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="H55" s="45" t="s">
+      <c r="H55" s="39" t="s">
         <v>167</v>
       </c>
-      <c r="I55" s="45" t="s">
+      <c r="I55" s="39" t="s">
         <v>202</v>
       </c>
-      <c r="K55" s="35" t="s">
+      <c r="K55" s="32" t="s">
         <v>407</v>
       </c>
-      <c r="L55" s="35" t="s">
+      <c r="L55" s="32" t="s">
         <v>260</v>
       </c>
-      <c r="N55" s="35" t="s">
+      <c r="N55" s="32" t="s">
         <v>383</v>
       </c>
-      <c r="O55" s="36" t="s">
+      <c r="O55" s="33" t="s">
         <v>332</v>
       </c>
-      <c r="Q55" s="34" t="s">
+      <c r="Q55" s="31" t="s">
         <v>351</v>
       </c>
-      <c r="R55" s="40" t="s">
+      <c r="R55" s="35" t="s">
         <v>126</v>
       </c>
-      <c r="T55" s="35" t="s">
+      <c r="T55" s="32" t="s">
         <v>267</v>
       </c>
-      <c r="U55" s="35" t="s">
+      <c r="U55" s="32" t="s">
         <v>346</v>
       </c>
     </row>
     <row r="56" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="34" t="s">
+      <c r="B56" s="31" t="s">
         <v>396</v>
       </c>
-      <c r="C56" s="34" t="s">
+      <c r="C56" s="31" t="s">
         <v>253</v>
       </c>
-      <c r="D56" s="42" t="s">
+      <c r="D56" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="E56" s="35" t="s">
+      <c r="E56" s="32" t="s">
         <v>375</v>
       </c>
-      <c r="G56" s="44" t="s">
+      <c r="G56" s="38" t="s">
         <v>42</v>
       </c>
-      <c r="H56" s="45" t="s">
+      <c r="H56" s="39" t="s">
         <v>203</v>
       </c>
-      <c r="I56" s="45" t="s">
+      <c r="I56" s="39" t="s">
         <v>190</v>
       </c>
-      <c r="K56" s="35" t="s">
+      <c r="K56" s="32" t="s">
         <v>407</v>
       </c>
-      <c r="L56" s="35" t="s">
+      <c r="L56" s="32" t="s">
         <v>251</v>
       </c>
-      <c r="N56" s="35" t="s">
+      <c r="N56" s="32" t="s">
         <v>384</v>
       </c>
-      <c r="O56" s="36" t="s">
+      <c r="O56" s="33" t="s">
         <v>333</v>
       </c>
-      <c r="Q56" s="34" t="s">
+      <c r="Q56" s="31" t="s">
         <v>352</v>
       </c>
-      <c r="R56" s="40" t="s">
+      <c r="R56" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="T56" s="35" t="s">
+      <c r="T56" s="32" t="s">
         <v>267</v>
       </c>
-      <c r="U56" s="35" t="s">
+      <c r="U56" s="32" t="s">
         <v>352</v>
       </c>
     </row>
     <row r="57" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="34" t="s">
+      <c r="B57" s="31" t="s">
         <v>397</v>
       </c>
-      <c r="C57" s="34" t="s">
+      <c r="C57" s="31" t="s">
         <v>254</v>
       </c>
-      <c r="D57" s="44" t="s">
+      <c r="D57" s="38" t="s">
         <v>42</v>
       </c>
-      <c r="E57" s="35" t="s">
+      <c r="E57" s="32" t="s">
         <v>376</v>
       </c>
-      <c r="G57" s="44" t="s">
+      <c r="G57" s="38" t="s">
         <v>57</v>
       </c>
-      <c r="H57" s="45" t="s">
+      <c r="H57" s="39" t="s">
         <v>204</v>
       </c>
-      <c r="I57" s="45" t="s">
+      <c r="I57" s="39" t="s">
         <v>188</v>
       </c>
-      <c r="K57" s="35" t="s">
+      <c r="K57" s="32" t="s">
         <v>408</v>
       </c>
-      <c r="L57" s="35" t="s">
+      <c r="L57" s="32" t="s">
         <v>255</v>
       </c>
-      <c r="N57" s="35" t="s">
+      <c r="N57" s="32" t="s">
         <v>385</v>
       </c>
-      <c r="O57" s="36" t="s">
+      <c r="O57" s="33" t="s">
         <v>334</v>
       </c>
-      <c r="T57" s="35" t="s">
+      <c r="T57" s="32" t="s">
         <v>268</v>
       </c>
-      <c r="U57" s="35" t="s">
+      <c r="U57" s="32" t="s">
         <v>351</v>
       </c>
     </row>
     <row r="58" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="34" t="s">
+      <c r="B58" s="31" t="s">
         <v>398</v>
       </c>
-      <c r="C58" s="34" t="s">
+      <c r="C58" s="31" t="s">
         <v>255</v>
       </c>
-      <c r="D58" s="42" t="s">
+      <c r="D58" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="E58" s="35" t="s">
+      <c r="E58" s="32" t="s">
         <v>377</v>
       </c>
-      <c r="K58" s="35" t="s">
+      <c r="K58" s="32" t="s">
         <v>409</v>
       </c>
-      <c r="L58" s="35" t="s">
+      <c r="L58" s="32" t="s">
         <v>252</v>
       </c>
-      <c r="N58" s="35" t="s">
+      <c r="N58" s="32" t="s">
         <v>386</v>
       </c>
-      <c r="O58" s="36" t="s">
+      <c r="O58" s="33" t="s">
         <v>335</v>
       </c>
-      <c r="T58" s="35" t="s">
+      <c r="T58" s="32" t="s">
         <v>269</v>
       </c>
-      <c r="U58" s="35" t="s">
+      <c r="U58" s="32" t="s">
         <v>348</v>
       </c>
     </row>
     <row r="59" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="34" t="s">
+      <c r="B59" s="31" t="s">
         <v>399</v>
       </c>
-      <c r="C59" s="34" t="s">
+      <c r="C59" s="31" t="s">
         <v>256</v>
       </c>
-      <c r="D59" s="44" t="s">
+      <c r="D59" s="38" t="s">
         <v>57</v>
       </c>
-      <c r="E59" s="35" t="s">
+      <c r="E59" s="32" t="s">
         <v>378</v>
       </c>
-      <c r="K59" s="35" t="s">
+      <c r="K59" s="32" t="s">
         <v>409</v>
       </c>
-      <c r="L59" s="35" t="s">
+      <c r="L59" s="32" t="s">
         <v>254</v>
       </c>
-      <c r="N59" s="35" t="s">
+      <c r="N59" s="32" t="s">
         <v>387</v>
       </c>
-      <c r="O59" s="36" t="s">
+      <c r="O59" s="33" t="s">
         <v>336</v>
       </c>
-      <c r="T59" s="35" t="s">
+      <c r="T59" s="32" t="s">
         <v>269</v>
       </c>
-      <c r="U59" s="35" t="s">
+      <c r="U59" s="32" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="60" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="34" t="s">
+      <c r="B60" s="31" t="s">
         <v>400</v>
       </c>
-      <c r="C60" s="34" t="s">
+      <c r="C60" s="31" t="s">
         <v>257</v>
       </c>
-      <c r="D60" s="42" t="s">
+      <c r="D60" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="E60" s="35" t="s">
+      <c r="E60" s="32" t="s">
         <v>379</v>
       </c>
-      <c r="K60" s="35" t="s">
+      <c r="K60" s="32" t="s">
         <v>410</v>
       </c>
-      <c r="L60" s="35" t="s">
+      <c r="L60" s="32" t="s">
         <v>258</v>
       </c>
-      <c r="N60" s="35" t="s">
+      <c r="N60" s="32" t="s">
         <v>388</v>
       </c>
-      <c r="O60" s="36" t="s">
+      <c r="O60" s="33" t="s">
         <v>337</v>
       </c>
-      <c r="T60" s="35" t="s">
+      <c r="T60" s="32" t="s">
         <v>270</v>
       </c>
-      <c r="U60" s="35" t="s">
+      <c r="U60" s="32" t="s">
         <v>349</v>
       </c>
     </row>
     <row r="61" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="34" t="s">
+      <c r="B61" s="31" t="s">
         <v>401</v>
       </c>
-      <c r="C61" s="34" t="s">
+      <c r="C61" s="31" t="s">
         <v>258</v>
       </c>
-      <c r="D61" s="44" t="s">
+      <c r="D61" s="38" t="s">
         <v>42</v>
       </c>
-      <c r="E61" s="35" t="s">
+      <c r="E61" s="32" t="s">
         <v>380</v>
       </c>
-      <c r="K61" s="35" t="s">
+      <c r="K61" s="32" t="s">
         <v>410</v>
       </c>
-      <c r="L61" s="35" t="s">
+      <c r="L61" s="32" t="s">
         <v>257</v>
       </c>
-      <c r="N61" s="35" t="s">
+      <c r="N61" s="32" t="s">
         <v>389</v>
       </c>
-      <c r="O61" s="36" t="s">
+      <c r="O61" s="33" t="s">
         <v>338</v>
       </c>
-      <c r="T61" s="35" t="s">
+      <c r="T61" s="32" t="s">
         <v>270</v>
       </c>
-      <c r="U61" s="35" t="s">
+      <c r="U61" s="32" t="s">
         <v>346</v>
       </c>
     </row>
     <row r="62" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="34" t="s">
+      <c r="B62" s="31" t="s">
         <v>402</v>
       </c>
-      <c r="C62" s="34" t="s">
+      <c r="C62" s="31" t="s">
         <v>259</v>
       </c>
-      <c r="D62" s="42" t="s">
+      <c r="D62" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="E62" s="35" t="s">
+      <c r="E62" s="32" t="s">
         <v>381</v>
       </c>
-      <c r="K62" s="35" t="s">
+      <c r="K62" s="32" t="s">
         <v>411</v>
       </c>
-      <c r="L62" s="35" t="s">
+      <c r="L62" s="32" t="s">
         <v>256</v>
       </c>
-      <c r="N62" s="35" t="s">
+      <c r="N62" s="32" t="s">
         <v>390</v>
       </c>
-      <c r="O62" s="36" t="s">
+      <c r="O62" s="33" t="s">
         <v>339</v>
       </c>
     </row>
     <row r="63" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B63" s="34" t="s">
+      <c r="B63" s="31" t="s">
         <v>403</v>
       </c>
-      <c r="C63" s="34" t="s">
+      <c r="C63" s="31" t="s">
         <v>260</v>
       </c>
-      <c r="D63" s="44" t="s">
+      <c r="D63" s="38" t="s">
         <v>57</v>
       </c>
-      <c r="E63" s="35" t="s">
+      <c r="E63" s="32" t="s">
         <v>382</v>
       </c>
-      <c r="K63" s="35" t="s">
+      <c r="K63" s="32" t="s">
         <v>412</v>
       </c>
-      <c r="L63" s="35" t="s">
+      <c r="L63" s="32" t="s">
         <v>253</v>
       </c>
-      <c r="N63" s="35" t="s">
+      <c r="N63" s="32" t="s">
         <v>391</v>
       </c>
-      <c r="O63" s="36" t="s">
+      <c r="O63" s="33" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="64" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B64" s="34" t="s">
+      <c r="B64" s="31" t="s">
         <v>404</v>
       </c>
-      <c r="C64" s="34" t="s">
+      <c r="C64" s="31" t="s">
         <v>261</v>
       </c>
-      <c r="D64" s="42" t="s">
+      <c r="D64" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="E64" s="35" t="s">
+      <c r="E64" s="32" t="s">
         <v>383</v>
       </c>
-      <c r="K64" s="35" t="s">
+      <c r="K64" s="32" t="s">
         <v>412</v>
       </c>
-      <c r="L64" s="35" t="s">
+      <c r="L64" s="32" t="s">
         <v>255</v>
       </c>
-      <c r="N64" s="35" t="s">
+      <c r="N64" s="32" t="s">
         <v>392</v>
       </c>
-      <c r="O64" s="36" t="s">
+      <c r="O64" s="33" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="65" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B65" s="34" t="s">
+      <c r="B65" s="31" t="s">
         <v>405</v>
       </c>
-      <c r="C65" s="34" t="s">
+      <c r="C65" s="31" t="s">
         <v>262</v>
       </c>
-      <c r="D65" s="44" t="s">
+      <c r="D65" s="38" t="s">
         <v>42</v>
       </c>
-      <c r="E65" s="35" t="s">
+      <c r="E65" s="32" t="s">
         <v>384</v>
       </c>
-      <c r="K65" s="35" t="s">
+      <c r="K65" s="32" t="s">
         <v>413</v>
       </c>
-      <c r="L65" s="35" t="s">
+      <c r="L65" s="32" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="66" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B66" s="34" t="s">
+      <c r="B66" s="31" t="s">
         <v>406</v>
       </c>
-      <c r="C66" s="34" t="s">
+      <c r="C66" s="31" t="s">
         <v>263</v>
       </c>
-      <c r="D66" s="42" t="s">
+      <c r="D66" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="E66" s="35" t="s">
+      <c r="E66" s="32" t="s">
         <v>385</v>
       </c>
-      <c r="K66" s="35" t="s">
+      <c r="K66" s="32" t="s">
         <v>413</v>
       </c>
-      <c r="L66" s="35" t="s">
+      <c r="L66" s="32" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="67" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="34" t="s">
+      <c r="B67" s="31" t="s">
         <v>407</v>
       </c>
-      <c r="C67" s="34" t="s">
+      <c r="C67" s="31" t="s">
         <v>264</v>
       </c>
-      <c r="D67" s="44" t="s">
+      <c r="D67" s="38" t="s">
         <v>57</v>
       </c>
-      <c r="E67" s="35" t="s">
+      <c r="E67" s="32" t="s">
         <v>386</v>
       </c>
     </row>
     <row r="68" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B68" s="34" t="s">
+      <c r="B68" s="31" t="s">
         <v>408</v>
       </c>
-      <c r="C68" s="34" t="s">
+      <c r="C68" s="31" t="s">
         <v>265</v>
       </c>
-      <c r="D68" s="42" t="s">
+      <c r="D68" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="E68" s="35" t="s">
+      <c r="E68" s="32" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="69" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="34" t="s">
+      <c r="B69" s="31" t="s">
         <v>409</v>
       </c>
-      <c r="C69" s="34" t="s">
+      <c r="C69" s="31" t="s">
         <v>266</v>
       </c>
-      <c r="D69" s="44" t="s">
+      <c r="D69" s="38" t="s">
         <v>42</v>
       </c>
-      <c r="E69" s="35" t="s">
+      <c r="E69" s="32" t="s">
         <v>388</v>
       </c>
     </row>
     <row r="70" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B70" s="34" t="s">
+      <c r="B70" s="31" t="s">
         <v>410</v>
       </c>
-      <c r="C70" s="34" t="s">
+      <c r="C70" s="31" t="s">
         <v>267</v>
       </c>
-      <c r="D70" s="42" t="s">
+      <c r="D70" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="E70" s="35" t="s">
+      <c r="E70" s="32" t="s">
         <v>389</v>
       </c>
     </row>
     <row r="71" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B71" s="34" t="s">
+      <c r="B71" s="31" t="s">
         <v>411</v>
       </c>
-      <c r="C71" s="34" t="s">
+      <c r="C71" s="31" t="s">
         <v>268</v>
       </c>
-      <c r="D71" s="44" t="s">
+      <c r="D71" s="38" t="s">
         <v>57</v>
       </c>
-      <c r="E71" s="35" t="s">
+      <c r="E71" s="32" t="s">
         <v>390</v>
       </c>
     </row>
     <row r="72" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B72" s="34" t="s">
+      <c r="B72" s="31" t="s">
         <v>412</v>
       </c>
-      <c r="C72" s="34" t="s">
+      <c r="C72" s="31" t="s">
         <v>269</v>
       </c>
-      <c r="D72" s="42" t="s">
+      <c r="D72" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="E72" s="35" t="s">
+      <c r="E72" s="32" t="s">
         <v>391</v>
       </c>
     </row>
     <row r="73" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B73" s="34" t="s">
+      <c r="B73" s="31" t="s">
         <v>413</v>
       </c>
-      <c r="C73" s="34" t="s">
+      <c r="C73" s="31" t="s">
         <v>270</v>
       </c>
-      <c r="D73" s="44" t="s">
+      <c r="D73" s="38" t="s">
         <v>42</v>
       </c>
-      <c r="E73" s="35" t="s">
+      <c r="E73" s="32" t="s">
         <v>392</v>
       </c>
     </row>
@@ -7716,13 +7716,13 @@
   </sheetData>
   <dataConsolidate/>
   <mergeCells count="7">
+    <mergeCell ref="B26:H26"/>
+    <mergeCell ref="K26:L26"/>
     <mergeCell ref="N26:O26"/>
     <mergeCell ref="Q26:R26"/>
     <mergeCell ref="K33:L33"/>
     <mergeCell ref="N43:O43"/>
     <mergeCell ref="Q48:R48"/>
-    <mergeCell ref="B26:H26"/>
-    <mergeCell ref="K26:L26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7742,7 +7742,7 @@
     <col min="13" max="13" width="19.42578125" customWidth="1"/>
     <col min="14" max="14" width="13.42578125" customWidth="1"/>
     <col min="18" max="18" width="18.7109375" customWidth="1"/>
-    <col min="19" max="19" width="17.7109375" customWidth="1"/>
+    <col min="19" max="19" width="19.7109375" customWidth="1"/>
     <col min="20" max="20" width="15" customWidth="1"/>
     <col min="21" max="21" width="14.7109375" customWidth="1"/>
     <col min="22" max="22" width="16.85546875" customWidth="1"/>
@@ -9075,2004 +9075,2004 @@
     <row r="24" spans="1:23" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="25" spans="1:23" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="26" spans="1:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="46" t="s">
+      <c r="B26" s="60" t="s">
         <v>233</v>
       </c>
-      <c r="C26" s="46"/>
-      <c r="D26" s="46"/>
-      <c r="E26" s="46"/>
-      <c r="F26" s="46"/>
-      <c r="G26" s="46"/>
-      <c r="H26" s="46"/>
-      <c r="J26" s="50" t="s">
+      <c r="C26" s="60"/>
+      <c r="D26" s="60"/>
+      <c r="E26" s="60"/>
+      <c r="F26" s="60"/>
+      <c r="G26" s="60"/>
+      <c r="H26" s="60"/>
+      <c r="J26" s="65" t="s">
         <v>426</v>
       </c>
-      <c r="K26" s="50"/>
+      <c r="K26" s="65"/>
       <c r="M26" s="72" t="s">
         <v>416</v>
       </c>
       <c r="N26" s="73"/>
       <c r="O26" s="74"/>
-      <c r="Q26" s="37" t="s">
+      <c r="Q26" s="66" t="s">
         <v>278</v>
       </c>
-      <c r="R26" s="37"/>
+      <c r="R26" s="66"/>
       <c r="S26" s="29"/>
-      <c r="T26" s="33" t="s">
+      <c r="T26" s="64" t="s">
         <v>275</v>
       </c>
-      <c r="U26" s="33"/>
-      <c r="V26" s="33"/>
-      <c r="W26" s="33"/>
+      <c r="U26" s="64"/>
+      <c r="V26" s="64"/>
+      <c r="W26" s="64"/>
     </row>
     <row r="27" spans="1:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="47" t="s">
+      <c r="B27" s="40" t="s">
         <v>234</v>
       </c>
-      <c r="C27" s="47" t="s">
+      <c r="C27" s="40" t="s">
         <v>235</v>
       </c>
-      <c r="D27" s="47" t="s">
+      <c r="D27" s="40" t="s">
         <v>201</v>
       </c>
-      <c r="E27" s="47" t="s">
+      <c r="E27" s="40" t="s">
         <v>248</v>
       </c>
-      <c r="F27" s="47" t="s">
+      <c r="F27" s="40" t="s">
         <v>250</v>
       </c>
-      <c r="G27" s="47" t="s">
+      <c r="G27" s="40" t="s">
         <v>236</v>
       </c>
-      <c r="H27" s="47" t="s">
+      <c r="H27" s="40" t="s">
         <v>237</v>
       </c>
-      <c r="J27" s="47" t="s">
+      <c r="J27" s="40" t="s">
         <v>249</v>
       </c>
-      <c r="K27" s="47" t="s">
+      <c r="K27" s="40" t="s">
         <v>238</v>
       </c>
-      <c r="M27" s="75" t="s">
+      <c r="M27" s="48" t="s">
         <v>432</v>
       </c>
-      <c r="N27" s="52" t="s">
+      <c r="N27" s="43" t="s">
         <v>417</v>
       </c>
-      <c r="O27" s="52" t="s">
+      <c r="O27" s="43" t="s">
         <v>418</v>
       </c>
-      <c r="Q27" s="35" t="s">
+      <c r="Q27" s="32" t="s">
         <v>280</v>
       </c>
-      <c r="R27" s="35" t="s">
+      <c r="R27" s="32" t="s">
         <v>281</v>
       </c>
-      <c r="T27" s="70" t="s">
+      <c r="T27" s="47" t="s">
         <v>276</v>
       </c>
-      <c r="U27" s="70" t="s">
+      <c r="U27" s="47" t="s">
         <v>424</v>
       </c>
-      <c r="V27" s="70" t="s">
+      <c r="V27" s="47" t="s">
         <v>279</v>
       </c>
-      <c r="W27" s="70" t="s">
+      <c r="W27" s="47" t="s">
         <v>425</v>
       </c>
     </row>
     <row r="28" spans="1:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="34" t="s">
+      <c r="B28" s="31" t="s">
         <v>251</v>
       </c>
-      <c r="C28" s="43" t="s">
+      <c r="C28" s="37" t="s">
         <v>161</v>
       </c>
-      <c r="D28" s="43" t="s">
+      <c r="D28" s="37" t="s">
         <v>162</v>
       </c>
-      <c r="E28" s="42" t="s">
+      <c r="E28" s="36" t="s">
         <v>239</v>
       </c>
-      <c r="F28" s="48" t="s">
+      <c r="F28" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="G28" s="48" t="s">
+      <c r="G28" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="H28" s="43" t="s">
+      <c r="H28" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="J28" s="34" t="s">
+      <c r="J28" s="31" t="s">
         <v>239</v>
       </c>
-      <c r="K28" s="34" t="s">
+      <c r="K28" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="M28" s="34" t="s">
+      <c r="M28" s="31" t="s">
         <v>433</v>
       </c>
-      <c r="N28" s="35" t="s">
+      <c r="N28" s="32" t="s">
         <v>251</v>
       </c>
-      <c r="O28" s="35" t="s">
+      <c r="O28" s="32" t="s">
         <v>346</v>
       </c>
-      <c r="Q28" s="35" t="s">
+      <c r="Q28" s="32" t="s">
         <v>282</v>
       </c>
-      <c r="R28" s="35" t="s">
+      <c r="R28" s="32" t="s">
         <v>283</v>
       </c>
-      <c r="T28" s="35" t="s">
+      <c r="T28" s="32" t="s">
         <v>373</v>
       </c>
-      <c r="U28" s="35" t="s">
+      <c r="U28" s="32" t="s">
         <v>322</v>
       </c>
-      <c r="V28" s="35" t="s">
+      <c r="V28" s="32" t="s">
         <v>280</v>
       </c>
-      <c r="W28" s="35" t="s">
+      <c r="W28" s="32" t="s">
         <v>421</v>
       </c>
     </row>
     <row r="29" spans="1:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="34" t="s">
+      <c r="B29" s="31" t="s">
         <v>252</v>
       </c>
-      <c r="C29" s="45" t="s">
+      <c r="C29" s="39" t="s">
         <v>163</v>
       </c>
-      <c r="D29" s="45" t="s">
+      <c r="D29" s="39" t="s">
         <v>164</v>
       </c>
-      <c r="E29" s="44" t="s">
+      <c r="E29" s="38" t="s">
         <v>239</v>
       </c>
-      <c r="F29" s="49" t="s">
+      <c r="F29" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="G29" s="49" t="s">
+      <c r="G29" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="H29" s="45" t="s">
+      <c r="H29" s="39" t="s">
         <v>24</v>
       </c>
-      <c r="J29" s="34" t="s">
+      <c r="J29" s="31" t="s">
         <v>240</v>
       </c>
-      <c r="K29" s="34" t="s">
+      <c r="K29" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="M29" s="34" t="s">
+      <c r="M29" s="31" t="s">
         <v>434</v>
       </c>
-      <c r="N29" s="35" t="s">
+      <c r="N29" s="32" t="s">
         <v>251</v>
       </c>
-      <c r="O29" s="35" t="s">
+      <c r="O29" s="32" t="s">
         <v>347</v>
       </c>
-      <c r="Q29" s="35" t="s">
+      <c r="Q29" s="32" t="s">
         <v>284</v>
       </c>
-      <c r="R29" s="35" t="s">
+      <c r="R29" s="32" t="s">
         <v>285</v>
       </c>
-      <c r="T29" s="35" t="s">
+      <c r="T29" s="32" t="s">
         <v>374</v>
       </c>
-      <c r="U29" s="35" t="s">
+      <c r="U29" s="32" t="s">
         <v>323</v>
       </c>
-      <c r="V29" s="35" t="s">
+      <c r="V29" s="32" t="s">
         <v>282</v>
       </c>
-      <c r="W29" s="35" t="s">
+      <c r="W29" s="32" t="s">
         <v>421</v>
       </c>
     </row>
     <row r="30" spans="1:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="34" t="s">
+      <c r="B30" s="31" t="s">
         <v>253</v>
       </c>
-      <c r="C30" s="43" t="s">
+      <c r="C30" s="37" t="s">
         <v>165</v>
       </c>
-      <c r="D30" s="43" t="s">
+      <c r="D30" s="37" t="s">
         <v>166</v>
       </c>
-      <c r="E30" s="42" t="s">
+      <c r="E30" s="36" t="s">
         <v>240</v>
       </c>
-      <c r="F30" s="48" t="s">
+      <c r="F30" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="G30" s="48" t="s">
+      <c r="G30" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="H30" s="43" t="s">
+      <c r="H30" s="37" t="s">
         <v>33</v>
       </c>
-      <c r="J30" s="34" t="s">
+      <c r="J30" s="31" t="s">
         <v>241</v>
       </c>
-      <c r="K30" s="34" t="s">
+      <c r="K30" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="M30" s="34" t="s">
+      <c r="M30" s="31" t="s">
         <v>435</v>
       </c>
-      <c r="N30" s="35" t="s">
+      <c r="N30" s="32" t="s">
         <v>252</v>
       </c>
-      <c r="O30" s="35" t="s">
+      <c r="O30" s="32" t="s">
         <v>348</v>
       </c>
-      <c r="Q30" s="35" t="s">
+      <c r="Q30" s="32" t="s">
         <v>286</v>
       </c>
-      <c r="R30" s="35" t="s">
+      <c r="R30" s="32" t="s">
         <v>287</v>
       </c>
-      <c r="T30" s="35" t="s">
+      <c r="T30" s="32" t="s">
         <v>375</v>
       </c>
-      <c r="U30" s="35" t="s">
+      <c r="U30" s="32" t="s">
         <v>324</v>
       </c>
-      <c r="V30" s="35" t="s">
+      <c r="V30" s="32" t="s">
         <v>284</v>
       </c>
-      <c r="W30" s="35" t="s">
+      <c r="W30" s="32" t="s">
         <v>422</v>
       </c>
     </row>
     <row r="31" spans="1:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="34" t="s">
+      <c r="B31" s="31" t="s">
         <v>254</v>
       </c>
-      <c r="C31" s="45" t="s">
+      <c r="C31" s="39" t="s">
         <v>167</v>
       </c>
-      <c r="D31" s="45" t="s">
+      <c r="D31" s="39" t="s">
         <v>168</v>
       </c>
-      <c r="E31" s="44" t="s">
+      <c r="E31" s="38" t="s">
         <v>239</v>
       </c>
-      <c r="F31" s="49" t="s">
+      <c r="F31" s="42" t="s">
         <v>38</v>
       </c>
-      <c r="G31" s="49" t="s">
+      <c r="G31" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="H31" s="45" t="s">
+      <c r="H31" s="39" t="s">
         <v>40</v>
       </c>
-      <c r="J31" s="34" t="s">
+      <c r="J31" s="31" t="s">
         <v>242</v>
       </c>
-      <c r="K31" s="34" t="s">
+      <c r="K31" s="31" t="s">
         <v>105</v>
       </c>
-      <c r="M31" s="34" t="s">
+      <c r="M31" s="31" t="s">
         <v>436</v>
       </c>
-      <c r="N31" s="35" t="s">
+      <c r="N31" s="32" t="s">
         <v>253</v>
       </c>
-      <c r="O31" s="35" t="s">
+      <c r="O31" s="32" t="s">
         <v>349</v>
       </c>
-      <c r="Q31" s="35" t="s">
+      <c r="Q31" s="32" t="s">
         <v>288</v>
       </c>
-      <c r="R31" s="35" t="s">
+      <c r="R31" s="32" t="s">
         <v>289</v>
       </c>
-      <c r="T31" s="35" t="s">
+      <c r="T31" s="32" t="s">
         <v>376</v>
       </c>
-      <c r="U31" s="35" t="s">
+      <c r="U31" s="32" t="s">
         <v>325</v>
       </c>
-      <c r="V31" s="35" t="s">
+      <c r="V31" s="32" t="s">
         <v>286</v>
       </c>
-      <c r="W31" s="35" t="s">
+      <c r="W31" s="32" t="s">
         <v>421</v>
       </c>
     </row>
     <row r="32" spans="1:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="34" t="s">
+      <c r="B32" s="31" t="s">
         <v>255</v>
       </c>
-      <c r="C32" s="43" t="s">
+      <c r="C32" s="37" t="s">
         <v>169</v>
       </c>
-      <c r="D32" s="43" t="s">
+      <c r="D32" s="37" t="s">
         <v>170</v>
       </c>
-      <c r="E32" s="42" t="s">
+      <c r="E32" s="36" t="s">
         <v>239</v>
       </c>
-      <c r="F32" s="48" t="s">
+      <c r="F32" s="41" t="s">
         <v>46</v>
       </c>
-      <c r="G32" s="48" t="s">
+      <c r="G32" s="41" t="s">
         <v>47</v>
       </c>
-      <c r="H32" s="43" t="s">
+      <c r="H32" s="37" t="s">
         <v>48</v>
       </c>
-      <c r="M32" s="34" t="s">
+      <c r="M32" s="31" t="s">
         <v>437</v>
       </c>
-      <c r="N32" s="35" t="s">
+      <c r="N32" s="32" t="s">
         <v>253</v>
       </c>
-      <c r="O32" s="35" t="s">
+      <c r="O32" s="32" t="s">
         <v>350</v>
       </c>
-      <c r="Q32" s="35" t="s">
+      <c r="Q32" s="32" t="s">
         <v>290</v>
       </c>
-      <c r="R32" s="35" t="s">
+      <c r="R32" s="32" t="s">
         <v>291</v>
       </c>
-      <c r="T32" s="35" t="s">
+      <c r="T32" s="32" t="s">
         <v>377</v>
       </c>
-      <c r="U32" s="35" t="s">
+      <c r="U32" s="32" t="s">
         <v>326</v>
       </c>
-      <c r="V32" s="35" t="s">
+      <c r="V32" s="32" t="s">
         <v>288</v>
       </c>
-      <c r="W32" s="35" t="s">
+      <c r="W32" s="32" t="s">
         <v>422</v>
       </c>
     </row>
     <row r="33" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="34" t="s">
+      <c r="B33" s="31" t="s">
         <v>256</v>
       </c>
-      <c r="C33" s="45" t="s">
+      <c r="C33" s="39" t="s">
         <v>171</v>
       </c>
-      <c r="D33" s="45" t="s">
+      <c r="D33" s="39" t="s">
         <v>172</v>
       </c>
-      <c r="E33" s="44" t="s">
+      <c r="E33" s="38" t="s">
         <v>241</v>
       </c>
-      <c r="F33" s="49" t="s">
+      <c r="F33" s="42" t="s">
         <v>53</v>
       </c>
-      <c r="G33" s="49" t="s">
+      <c r="G33" s="42" t="s">
         <v>54</v>
       </c>
-      <c r="H33" s="45" t="s">
+      <c r="H33" s="39" t="s">
         <v>55</v>
       </c>
-      <c r="M33" s="34" t="s">
+      <c r="M33" s="31" t="s">
         <v>438</v>
       </c>
-      <c r="N33" s="35" t="s">
+      <c r="N33" s="32" t="s">
         <v>254</v>
       </c>
-      <c r="O33" s="35" t="s">
+      <c r="O33" s="32" t="s">
         <v>351</v>
       </c>
-      <c r="Q33" s="35" t="s">
+      <c r="Q33" s="32" t="s">
         <v>292</v>
       </c>
-      <c r="R33" s="35" t="s">
+      <c r="R33" s="32" t="s">
         <v>293</v>
       </c>
-      <c r="T33" s="35" t="s">
+      <c r="T33" s="32" t="s">
         <v>378</v>
       </c>
-      <c r="U33" s="35" t="s">
+      <c r="U33" s="32" t="s">
         <v>327</v>
       </c>
-      <c r="V33" s="35" t="s">
+      <c r="V33" s="32" t="s">
         <v>290</v>
       </c>
-      <c r="W33" s="35" t="s">
+      <c r="W33" s="32" t="s">
         <v>423</v>
       </c>
     </row>
     <row r="34" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="34" t="s">
+      <c r="B34" s="31" t="s">
         <v>257</v>
       </c>
-      <c r="C34" s="43" t="s">
+      <c r="C34" s="37" t="s">
         <v>173</v>
       </c>
-      <c r="D34" s="43" t="s">
+      <c r="D34" s="37" t="s">
         <v>174</v>
       </c>
-      <c r="E34" s="42" t="s">
+      <c r="E34" s="36" t="s">
         <v>239</v>
       </c>
-      <c r="F34" s="48" t="s">
+      <c r="F34" s="41" t="s">
         <v>62</v>
       </c>
-      <c r="G34" s="48" t="s">
+      <c r="G34" s="41" t="s">
         <v>63</v>
       </c>
-      <c r="H34" s="43" t="s">
+      <c r="H34" s="37" t="s">
         <v>64</v>
       </c>
-      <c r="J34" s="51" t="s">
+      <c r="J34" s="68" t="s">
         <v>343</v>
       </c>
-      <c r="K34" s="51"/>
-      <c r="M34" s="34" t="s">
+      <c r="K34" s="68"/>
+      <c r="M34" s="31" t="s">
         <v>439</v>
       </c>
-      <c r="N34" s="35" t="s">
+      <c r="N34" s="32" t="s">
         <v>254</v>
       </c>
-      <c r="O34" s="35" t="s">
+      <c r="O34" s="32" t="s">
         <v>346</v>
       </c>
-      <c r="Q34" s="35" t="s">
+      <c r="Q34" s="32" t="s">
         <v>294</v>
       </c>
-      <c r="R34" s="35" t="s">
+      <c r="R34" s="32" t="s">
         <v>295</v>
       </c>
-      <c r="T34" s="35" t="s">
+      <c r="T34" s="32" t="s">
         <v>379</v>
       </c>
-      <c r="U34" s="35" t="s">
+      <c r="U34" s="32" t="s">
         <v>328</v>
       </c>
-      <c r="V34" s="35" t="s">
+      <c r="V34" s="32" t="s">
         <v>292</v>
       </c>
-      <c r="W34" s="35" t="s">
+      <c r="W34" s="32" t="s">
         <v>422</v>
       </c>
     </row>
     <row r="35" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="34" t="s">
+      <c r="B35" s="31" t="s">
         <v>258</v>
       </c>
-      <c r="C35" s="45" t="s">
+      <c r="C35" s="39" t="s">
         <v>175</v>
       </c>
-      <c r="D35" s="45" t="s">
+      <c r="D35" s="39" t="s">
         <v>176</v>
       </c>
-      <c r="E35" s="44" t="s">
+      <c r="E35" s="38" t="s">
         <v>239</v>
       </c>
-      <c r="F35" s="49" t="s">
+      <c r="F35" s="42" t="s">
         <v>68</v>
       </c>
-      <c r="G35" s="49" t="s">
+      <c r="G35" s="42" t="s">
         <v>69</v>
       </c>
-      <c r="H35" s="45" t="s">
+      <c r="H35" s="39" t="s">
         <v>70</v>
       </c>
-      <c r="J35" s="34" t="s">
+      <c r="J35" s="31" t="s">
         <v>344</v>
       </c>
-      <c r="K35" s="34" t="s">
+      <c r="K35" s="31" t="s">
         <v>345</v>
       </c>
-      <c r="M35" s="34" t="s">
+      <c r="M35" s="31" t="s">
         <v>440</v>
       </c>
-      <c r="N35" s="35" t="s">
+      <c r="N35" s="32" t="s">
         <v>255</v>
       </c>
-      <c r="O35" s="35" t="s">
+      <c r="O35" s="32" t="s">
         <v>352</v>
       </c>
-      <c r="Q35" s="35" t="s">
+      <c r="Q35" s="32" t="s">
         <v>296</v>
       </c>
-      <c r="R35" s="35" t="s">
+      <c r="R35" s="32" t="s">
         <v>297</v>
       </c>
-      <c r="T35" s="35" t="s">
+      <c r="T35" s="32" t="s">
         <v>380</v>
       </c>
-      <c r="U35" s="35" t="s">
+      <c r="U35" s="32" t="s">
         <v>329</v>
       </c>
-      <c r="V35" s="35" t="s">
+      <c r="V35" s="32" t="s">
         <v>294</v>
       </c>
-      <c r="W35" s="35" t="s">
+      <c r="W35" s="32" t="s">
         <v>421</v>
       </c>
     </row>
     <row r="36" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="34" t="s">
+      <c r="B36" s="31" t="s">
         <v>259</v>
       </c>
-      <c r="C36" s="43" t="s">
+      <c r="C36" s="37" t="s">
         <v>177</v>
       </c>
-      <c r="D36" s="43" t="s">
+      <c r="D36" s="37" t="s">
         <v>178</v>
       </c>
-      <c r="E36" s="42" t="s">
+      <c r="E36" s="36" t="s">
         <v>240</v>
       </c>
-      <c r="F36" s="48" t="s">
+      <c r="F36" s="41" t="s">
         <v>73</v>
       </c>
-      <c r="G36" s="48" t="s">
+      <c r="G36" s="41" t="s">
         <v>74</v>
       </c>
-      <c r="H36" s="43" t="s">
+      <c r="H36" s="37" t="s">
         <v>75</v>
       </c>
-      <c r="J36" s="34" t="s">
+      <c r="J36" s="31" t="s">
         <v>346</v>
       </c>
-      <c r="K36" s="40" t="s">
+      <c r="K36" s="35" t="s">
         <v>82</v>
       </c>
-      <c r="M36" s="34" t="s">
+      <c r="M36" s="31" t="s">
         <v>441</v>
       </c>
-      <c r="N36" s="35" t="s">
+      <c r="N36" s="32" t="s">
         <v>256</v>
       </c>
-      <c r="O36" s="35" t="s">
+      <c r="O36" s="32" t="s">
         <v>348</v>
       </c>
-      <c r="Q36" s="35" t="s">
+      <c r="Q36" s="32" t="s">
         <v>298</v>
       </c>
-      <c r="R36" s="35" t="s">
+      <c r="R36" s="32" t="s">
         <v>299</v>
       </c>
-      <c r="T36" s="35" t="s">
+      <c r="T36" s="32" t="s">
         <v>381</v>
       </c>
-      <c r="U36" s="35" t="s">
+      <c r="U36" s="32" t="s">
         <v>330</v>
       </c>
-      <c r="V36" s="35" t="s">
+      <c r="V36" s="32" t="s">
         <v>296</v>
       </c>
-      <c r="W36" s="35" t="s">
+      <c r="W36" s="32" t="s">
         <v>422</v>
       </c>
     </row>
     <row r="37" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="34" t="s">
+      <c r="B37" s="31" t="s">
         <v>260</v>
       </c>
-      <c r="C37" s="45" t="s">
+      <c r="C37" s="39" t="s">
         <v>179</v>
       </c>
-      <c r="D37" s="45" t="s">
+      <c r="D37" s="39" t="s">
         <v>180</v>
       </c>
-      <c r="E37" s="44" t="s">
+      <c r="E37" s="38" t="s">
         <v>239</v>
       </c>
-      <c r="F37" s="49" t="s">
+      <c r="F37" s="42" t="s">
         <v>79</v>
       </c>
-      <c r="G37" s="49" t="s">
+      <c r="G37" s="42" t="s">
         <v>80</v>
       </c>
-      <c r="H37" s="45" t="s">
+      <c r="H37" s="39" t="s">
         <v>81</v>
       </c>
-      <c r="J37" s="34" t="s">
+      <c r="J37" s="31" t="s">
         <v>347</v>
       </c>
-      <c r="K37" s="40" t="s">
+      <c r="K37" s="35" t="s">
         <v>211</v>
       </c>
-      <c r="M37" s="34" t="s">
+      <c r="M37" s="31" t="s">
         <v>442</v>
       </c>
-      <c r="N37" s="35" t="s">
+      <c r="N37" s="32" t="s">
         <v>256</v>
       </c>
-      <c r="O37" s="35" t="s">
+      <c r="O37" s="32" t="s">
         <v>346</v>
       </c>
-      <c r="Q37" s="35" t="s">
+      <c r="Q37" s="32" t="s">
         <v>300</v>
       </c>
-      <c r="R37" s="35" t="s">
+      <c r="R37" s="32" t="s">
         <v>301</v>
       </c>
-      <c r="T37" s="35" t="s">
+      <c r="T37" s="32" t="s">
         <v>382</v>
       </c>
-      <c r="U37" s="35" t="s">
+      <c r="U37" s="32" t="s">
         <v>331</v>
       </c>
-      <c r="V37" s="35" t="s">
+      <c r="V37" s="32" t="s">
         <v>298</v>
       </c>
-      <c r="W37" s="35" t="s">
+      <c r="W37" s="32" t="s">
         <v>423</v>
       </c>
     </row>
     <row r="38" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="34" t="s">
+      <c r="B38" s="31" t="s">
         <v>261</v>
       </c>
-      <c r="C38" s="43" t="s">
+      <c r="C38" s="37" t="s">
         <v>181</v>
       </c>
-      <c r="D38" s="43" t="s">
+      <c r="D38" s="37" t="s">
         <v>182</v>
       </c>
-      <c r="E38" s="42" t="s">
+      <c r="E38" s="36" t="s">
         <v>239</v>
       </c>
-      <c r="F38" s="48" t="s">
+      <c r="F38" s="41" t="s">
         <v>85</v>
       </c>
-      <c r="G38" s="48" t="s">
+      <c r="G38" s="41" t="s">
         <v>86</v>
       </c>
-      <c r="H38" s="43" t="s">
+      <c r="H38" s="37" t="s">
         <v>87</v>
       </c>
-      <c r="J38" s="34" t="s">
+      <c r="J38" s="31" t="s">
         <v>348</v>
       </c>
-      <c r="K38" s="40" t="s">
+      <c r="K38" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="M38" s="34" t="s">
+      <c r="M38" s="31" t="s">
         <v>443</v>
       </c>
-      <c r="N38" s="35" t="s">
+      <c r="N38" s="32" t="s">
         <v>257</v>
       </c>
-      <c r="O38" s="35" t="s">
+      <c r="O38" s="32" t="s">
         <v>350</v>
       </c>
-      <c r="Q38" s="35" t="s">
+      <c r="Q38" s="32" t="s">
         <v>302</v>
       </c>
-      <c r="R38" s="35" t="s">
+      <c r="R38" s="32" t="s">
         <v>303</v>
       </c>
-      <c r="T38" s="35" t="s">
+      <c r="T38" s="32" t="s">
         <v>383</v>
       </c>
-      <c r="U38" s="35" t="s">
+      <c r="U38" s="32" t="s">
         <v>332</v>
       </c>
-      <c r="V38" s="35" t="s">
+      <c r="V38" s="32" t="s">
         <v>300</v>
       </c>
-      <c r="W38" s="35" t="s">
+      <c r="W38" s="32" t="s">
         <v>421</v>
       </c>
     </row>
     <row r="39" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="34" t="s">
+      <c r="B39" s="31" t="s">
         <v>262</v>
       </c>
-      <c r="C39" s="45" t="s">
+      <c r="C39" s="39" t="s">
         <v>183</v>
       </c>
-      <c r="D39" s="45" t="s">
+      <c r="D39" s="39" t="s">
         <v>184</v>
       </c>
-      <c r="E39" s="44" t="s">
+      <c r="E39" s="38" t="s">
         <v>241</v>
       </c>
-      <c r="F39" s="49" t="s">
+      <c r="F39" s="42" t="s">
         <v>91</v>
       </c>
-      <c r="G39" s="49" t="s">
+      <c r="G39" s="42" t="s">
         <v>92</v>
       </c>
-      <c r="H39" s="45" t="s">
+      <c r="H39" s="39" t="s">
         <v>93</v>
       </c>
-      <c r="J39" s="34" t="s">
+      <c r="J39" s="31" t="s">
         <v>349</v>
       </c>
-      <c r="K39" s="40" t="s">
+      <c r="K39" s="35" t="s">
         <v>71</v>
       </c>
-      <c r="M39" s="34" t="s">
+      <c r="M39" s="31" t="s">
         <v>444</v>
       </c>
-      <c r="N39" s="35" t="s">
+      <c r="N39" s="32" t="s">
         <v>257</v>
       </c>
-      <c r="O39" s="35" t="s">
+      <c r="O39" s="32" t="s">
         <v>347</v>
       </c>
-      <c r="Q39" s="35" t="s">
+      <c r="Q39" s="32" t="s">
         <v>304</v>
       </c>
-      <c r="R39" s="35" t="s">
+      <c r="R39" s="32" t="s">
         <v>305</v>
       </c>
-      <c r="T39" s="35" t="s">
+      <c r="T39" s="32" t="s">
         <v>384</v>
       </c>
-      <c r="U39" s="35" t="s">
+      <c r="U39" s="32" t="s">
         <v>333</v>
       </c>
-      <c r="V39" s="35" t="s">
+      <c r="V39" s="32" t="s">
         <v>302</v>
       </c>
-      <c r="W39" s="35" t="s">
+      <c r="W39" s="32" t="s">
         <v>423</v>
       </c>
     </row>
     <row r="40" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="34" t="s">
+      <c r="B40" s="31" t="s">
         <v>263</v>
       </c>
-      <c r="C40" s="43" t="s">
+      <c r="C40" s="37" t="s">
         <v>185</v>
       </c>
-      <c r="D40" s="43" t="s">
+      <c r="D40" s="37" t="s">
         <v>186</v>
       </c>
-      <c r="E40" s="42" t="s">
+      <c r="E40" s="36" t="s">
         <v>239</v>
       </c>
-      <c r="F40" s="48" t="s">
+      <c r="F40" s="41" t="s">
         <v>95</v>
       </c>
-      <c r="G40" s="48" t="s">
+      <c r="G40" s="41" t="s">
         <v>96</v>
       </c>
-      <c r="H40" s="43" t="s">
+      <c r="H40" s="37" t="s">
         <v>97</v>
       </c>
-      <c r="J40" s="34" t="s">
+      <c r="J40" s="31" t="s">
         <v>350</v>
       </c>
-      <c r="K40" s="40" t="s">
+      <c r="K40" s="35" t="s">
         <v>109</v>
       </c>
-      <c r="M40" s="34" t="s">
+      <c r="M40" s="31" t="s">
         <v>445</v>
       </c>
-      <c r="N40" s="35" t="s">
+      <c r="N40" s="32" t="s">
         <v>258</v>
       </c>
-      <c r="O40" s="35" t="s">
+      <c r="O40" s="32" t="s">
         <v>349</v>
       </c>
-      <c r="Q40" s="35" t="s">
+      <c r="Q40" s="32" t="s">
         <v>306</v>
       </c>
-      <c r="R40" s="35" t="s">
+      <c r="R40" s="32" t="s">
         <v>307</v>
       </c>
-      <c r="T40" s="35" t="s">
+      <c r="T40" s="32" t="s">
         <v>385</v>
       </c>
-      <c r="U40" s="35" t="s">
+      <c r="U40" s="32" t="s">
         <v>334</v>
       </c>
-      <c r="V40" s="35" t="s">
+      <c r="V40" s="32" t="s">
         <v>304</v>
       </c>
-      <c r="W40" s="35" t="s">
+      <c r="W40" s="32" t="s">
         <v>422</v>
       </c>
     </row>
     <row r="41" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="34" t="s">
+      <c r="B41" s="31" t="s">
         <v>264</v>
       </c>
-      <c r="C41" s="45" t="s">
+      <c r="C41" s="39" t="s">
         <v>187</v>
       </c>
-      <c r="D41" s="45" t="s">
+      <c r="D41" s="39" t="s">
         <v>188</v>
       </c>
-      <c r="E41" s="44" t="s">
+      <c r="E41" s="38" t="s">
         <v>239</v>
       </c>
-      <c r="F41" s="49" t="s">
+      <c r="F41" s="42" t="s">
         <v>101</v>
       </c>
-      <c r="G41" s="49" t="s">
+      <c r="G41" s="42" t="s">
         <v>102</v>
       </c>
-      <c r="H41" s="45" t="s">
+      <c r="H41" s="39" t="s">
         <v>103</v>
       </c>
-      <c r="J41" s="34" t="s">
+      <c r="J41" s="31" t="s">
         <v>351</v>
       </c>
-      <c r="K41" s="40" t="s">
+      <c r="K41" s="35" t="s">
         <v>126</v>
       </c>
-      <c r="M41" s="34" t="s">
+      <c r="M41" s="31" t="s">
         <v>446</v>
       </c>
-      <c r="N41" s="35" t="s">
+      <c r="N41" s="32" t="s">
         <v>259</v>
       </c>
-      <c r="O41" s="35" t="s">
+      <c r="O41" s="32" t="s">
         <v>351</v>
       </c>
-      <c r="Q41" s="35" t="s">
+      <c r="Q41" s="32" t="s">
         <v>308</v>
       </c>
-      <c r="R41" s="35" t="s">
+      <c r="R41" s="32" t="s">
         <v>309</v>
       </c>
-      <c r="T41" s="35" t="s">
+      <c r="T41" s="32" t="s">
         <v>386</v>
       </c>
-      <c r="U41" s="35" t="s">
+      <c r="U41" s="32" t="s">
         <v>335</v>
       </c>
-      <c r="V41" s="35" t="s">
+      <c r="V41" s="32" t="s">
         <v>306</v>
       </c>
-      <c r="W41" s="35" t="s">
+      <c r="W41" s="32" t="s">
         <v>421</v>
       </c>
     </row>
     <row r="42" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="34" t="s">
+      <c r="B42" s="31" t="s">
         <v>265</v>
       </c>
-      <c r="C42" s="43" t="s">
+      <c r="C42" s="37" t="s">
         <v>189</v>
       </c>
-      <c r="D42" s="43" t="s">
+      <c r="D42" s="37" t="s">
         <v>190</v>
       </c>
-      <c r="E42" s="42" t="s">
+      <c r="E42" s="36" t="s">
         <v>242</v>
       </c>
-      <c r="F42" s="48" t="s">
+      <c r="F42" s="41" t="s">
         <v>106</v>
       </c>
-      <c r="G42" s="48" t="s">
+      <c r="G42" s="41" t="s">
         <v>107</v>
       </c>
-      <c r="H42" s="43" t="s">
+      <c r="H42" s="37" t="s">
         <v>108</v>
       </c>
-      <c r="J42" s="34" t="s">
+      <c r="J42" s="31" t="s">
         <v>352</v>
       </c>
-      <c r="K42" s="40" t="s">
+      <c r="K42" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="M42" s="34" t="s">
+      <c r="M42" s="31" t="s">
         <v>447</v>
       </c>
-      <c r="N42" s="35" t="s">
+      <c r="N42" s="32" t="s">
         <v>259</v>
       </c>
-      <c r="O42" s="35" t="s">
+      <c r="O42" s="32" t="s">
         <v>352</v>
       </c>
-      <c r="Q42" s="35" t="s">
+      <c r="Q42" s="32" t="s">
         <v>310</v>
       </c>
-      <c r="R42" s="35" t="s">
+      <c r="R42" s="32" t="s">
         <v>311</v>
       </c>
-      <c r="T42" s="35" t="s">
+      <c r="T42" s="32" t="s">
         <v>387</v>
       </c>
-      <c r="U42" s="35" t="s">
+      <c r="U42" s="32" t="s">
         <v>336</v>
       </c>
-      <c r="V42" s="35" t="s">
+      <c r="V42" s="32" t="s">
         <v>308</v>
       </c>
-      <c r="W42" s="35" t="s">
+      <c r="W42" s="32" t="s">
         <v>422</v>
       </c>
     </row>
     <row r="43" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="34" t="s">
+      <c r="B43" s="31" t="s">
         <v>266</v>
       </c>
-      <c r="C43" s="45" t="s">
+      <c r="C43" s="39" t="s">
         <v>191</v>
       </c>
-      <c r="D43" s="45" t="s">
+      <c r="D43" s="39" t="s">
         <v>192</v>
       </c>
-      <c r="E43" s="44" t="s">
+      <c r="E43" s="38" t="s">
         <v>239</v>
       </c>
-      <c r="F43" s="49" t="s">
+      <c r="F43" s="42" t="s">
         <v>112</v>
       </c>
-      <c r="G43" s="49" t="s">
+      <c r="G43" s="42" t="s">
         <v>113</v>
       </c>
-      <c r="H43" s="45" t="s">
+      <c r="H43" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="M43" s="34" t="s">
+      <c r="M43" s="31" t="s">
         <v>448</v>
       </c>
-      <c r="N43" s="35" t="s">
+      <c r="N43" s="32" t="s">
         <v>260</v>
       </c>
-      <c r="O43" s="35" t="s">
+      <c r="O43" s="32" t="s">
         <v>346</v>
       </c>
-      <c r="Q43" s="35" t="s">
+      <c r="Q43" s="32" t="s">
         <v>312</v>
       </c>
-      <c r="R43" s="35" t="s">
+      <c r="R43" s="32" t="s">
         <v>313</v>
       </c>
-      <c r="T43" s="35" t="s">
+      <c r="T43" s="32" t="s">
         <v>388</v>
       </c>
-      <c r="U43" s="35" t="s">
+      <c r="U43" s="32" t="s">
         <v>337</v>
       </c>
-      <c r="V43" s="35" t="s">
+      <c r="V43" s="32" t="s">
         <v>310</v>
       </c>
-      <c r="W43" s="35" t="s">
+      <c r="W43" s="32" t="s">
         <v>421</v>
       </c>
     </row>
     <row r="44" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="34" t="s">
+      <c r="B44" s="31" t="s">
         <v>267</v>
       </c>
-      <c r="C44" s="43" t="s">
+      <c r="C44" s="37" t="s">
         <v>193</v>
       </c>
-      <c r="D44" s="43" t="s">
+      <c r="D44" s="37" t="s">
         <v>194</v>
       </c>
-      <c r="E44" s="42" t="s">
+      <c r="E44" s="36" t="s">
         <v>239</v>
       </c>
-      <c r="F44" s="48" t="s">
+      <c r="F44" s="41" t="s">
         <v>118</v>
       </c>
-      <c r="G44" s="48" t="s">
+      <c r="G44" s="41" t="s">
         <v>119</v>
       </c>
-      <c r="H44" s="43" t="s">
+      <c r="H44" s="37" t="s">
         <v>120</v>
       </c>
-      <c r="M44" s="34" t="s">
+      <c r="M44" s="31" t="s">
         <v>449</v>
       </c>
-      <c r="N44" s="35" t="s">
+      <c r="N44" s="32" t="s">
         <v>261</v>
       </c>
-      <c r="O44" s="35" t="s">
+      <c r="O44" s="32" t="s">
         <v>347</v>
       </c>
-      <c r="Q44" s="35" t="s">
+      <c r="Q44" s="32" t="s">
         <v>314</v>
       </c>
-      <c r="R44" s="35" t="s">
+      <c r="R44" s="32" t="s">
         <v>315</v>
       </c>
-      <c r="T44" s="35" t="s">
+      <c r="T44" s="32" t="s">
         <v>389</v>
       </c>
-      <c r="U44" s="35" t="s">
+      <c r="U44" s="32" t="s">
         <v>338</v>
       </c>
-      <c r="V44" s="35" t="s">
+      <c r="V44" s="32" t="s">
         <v>312</v>
       </c>
-      <c r="W44" s="35" t="s">
+      <c r="W44" s="32" t="s">
         <v>423</v>
       </c>
     </row>
     <row r="45" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="34" t="s">
+      <c r="B45" s="31" t="s">
         <v>268</v>
       </c>
-      <c r="C45" s="45" t="s">
+      <c r="C45" s="39" t="s">
         <v>195</v>
       </c>
-      <c r="D45" s="45" t="s">
+      <c r="D45" s="39" t="s">
         <v>196</v>
       </c>
-      <c r="E45" s="44" t="s">
+      <c r="E45" s="38" t="s">
         <v>239</v>
       </c>
-      <c r="F45" s="49" t="s">
+      <c r="F45" s="42" t="s">
         <v>124</v>
       </c>
-      <c r="G45" s="49" t="s">
+      <c r="G45" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="H45" s="45" t="s">
+      <c r="H45" s="39" t="s">
         <v>125</v>
       </c>
-      <c r="J45" s="38" t="s">
+      <c r="J45" s="69" t="s">
         <v>429</v>
       </c>
-      <c r="K45" s="38"/>
-      <c r="M45" s="34" t="s">
+      <c r="K45" s="69"/>
+      <c r="M45" s="31" t="s">
         <v>450</v>
       </c>
-      <c r="N45" s="35" t="s">
+      <c r="N45" s="32" t="s">
         <v>261</v>
       </c>
-      <c r="O45" s="35" t="s">
+      <c r="O45" s="32" t="s">
         <v>348</v>
       </c>
-      <c r="Q45" s="35" t="s">
+      <c r="Q45" s="32" t="s">
         <v>316</v>
       </c>
-      <c r="R45" s="35" t="s">
+      <c r="R45" s="32" t="s">
         <v>317</v>
       </c>
-      <c r="T45" s="35" t="s">
+      <c r="T45" s="32" t="s">
         <v>390</v>
       </c>
-      <c r="U45" s="35" t="s">
+      <c r="U45" s="32" t="s">
         <v>339</v>
       </c>
-      <c r="V45" s="35" t="s">
+      <c r="V45" s="32" t="s">
         <v>314</v>
       </c>
-      <c r="W45" s="35" t="s">
+      <c r="W45" s="32" t="s">
         <v>421</v>
       </c>
     </row>
     <row r="46" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="34" t="s">
+      <c r="B46" s="31" t="s">
         <v>269</v>
       </c>
-      <c r="C46" s="43" t="s">
+      <c r="C46" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="D46" s="43" t="s">
+      <c r="D46" s="37" t="s">
         <v>198</v>
       </c>
-      <c r="E46" s="42" t="s">
+      <c r="E46" s="36" t="s">
         <v>240</v>
       </c>
-      <c r="F46" s="48" t="s">
+      <c r="F46" s="41" t="s">
         <v>129</v>
       </c>
-      <c r="G46" s="48" t="s">
+      <c r="G46" s="41" t="s">
         <v>130</v>
       </c>
-      <c r="H46" s="43" t="s">
+      <c r="H46" s="37" t="s">
         <v>131</v>
       </c>
-      <c r="J46" s="39" t="s">
+      <c r="J46" s="34" t="s">
         <v>354</v>
       </c>
-      <c r="K46" s="39" t="s">
+      <c r="K46" s="34" t="s">
         <v>355</v>
       </c>
-      <c r="M46" s="34" t="s">
+      <c r="M46" s="31" t="s">
         <v>451</v>
       </c>
-      <c r="N46" s="35" t="s">
+      <c r="N46" s="32" t="s">
         <v>262</v>
       </c>
-      <c r="O46" s="35" t="s">
+      <c r="O46" s="32" t="s">
         <v>349</v>
       </c>
-      <c r="Q46" s="35" t="s">
+      <c r="Q46" s="32" t="s">
         <v>318</v>
       </c>
-      <c r="R46" s="35" t="s">
+      <c r="R46" s="32" t="s">
         <v>319</v>
       </c>
-      <c r="T46" s="35" t="s">
+      <c r="T46" s="32" t="s">
         <v>391</v>
       </c>
-      <c r="U46" s="35" t="s">
+      <c r="U46" s="32" t="s">
         <v>340</v>
       </c>
-      <c r="V46" s="35" t="s">
+      <c r="V46" s="32" t="s">
         <v>316</v>
       </c>
-      <c r="W46" s="35" t="s">
+      <c r="W46" s="32" t="s">
         <v>422</v>
       </c>
     </row>
     <row r="47" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="34" t="s">
+      <c r="B47" s="31" t="s">
         <v>270</v>
       </c>
-      <c r="C47" s="45" t="s">
+      <c r="C47" s="39" t="s">
         <v>199</v>
       </c>
-      <c r="D47" s="45" t="s">
+      <c r="D47" s="39" t="s">
         <v>200</v>
       </c>
-      <c r="E47" s="44" t="s">
+      <c r="E47" s="38" t="s">
         <v>239</v>
       </c>
-      <c r="F47" s="49" t="s">
+      <c r="F47" s="42" t="s">
         <v>135</v>
       </c>
-      <c r="G47" s="49" t="s">
+      <c r="G47" s="42" t="s">
         <v>136</v>
       </c>
-      <c r="H47" s="45" t="s">
+      <c r="H47" s="39" t="s">
         <v>137</v>
       </c>
-      <c r="J47" s="34" t="s">
+      <c r="J47" s="31" t="s">
         <v>251</v>
       </c>
-      <c r="K47" s="40" t="s">
+      <c r="K47" s="35" t="s">
         <v>363</v>
       </c>
-      <c r="M47" s="34" t="s">
+      <c r="M47" s="31" t="s">
         <v>452</v>
       </c>
-      <c r="N47" s="35" t="s">
+      <c r="N47" s="32" t="s">
         <v>262</v>
       </c>
-      <c r="O47" s="35" t="s">
+      <c r="O47" s="32" t="s">
         <v>350</v>
       </c>
-      <c r="T47" s="35" t="s">
+      <c r="T47" s="32" t="s">
         <v>392</v>
       </c>
-      <c r="U47" s="35" t="s">
+      <c r="U47" s="32" t="s">
         <v>341</v>
       </c>
-      <c r="V47" s="35" t="s">
+      <c r="V47" s="32" t="s">
         <v>318</v>
       </c>
-      <c r="W47" s="35" t="s">
+      <c r="W47" s="32" t="s">
         <v>423</v>
       </c>
     </row>
     <row r="48" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J48" s="34" t="s">
+      <c r="J48" s="31" t="s">
         <v>252</v>
       </c>
-      <c r="K48" s="40" t="s">
+      <c r="K48" s="35" t="s">
         <v>364</v>
       </c>
-      <c r="M48" s="34" t="s">
+      <c r="M48" s="31" t="s">
         <v>453</v>
       </c>
-      <c r="N48" s="35" t="s">
+      <c r="N48" s="32" t="s">
         <v>263</v>
       </c>
-      <c r="O48" s="35" t="s">
+      <c r="O48" s="32" t="s">
         <v>352</v>
       </c>
     </row>
     <row r="49" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J49" s="34" t="s">
+      <c r="J49" s="31" t="s">
         <v>253</v>
       </c>
-      <c r="K49" s="40" t="s">
+      <c r="K49" s="35" t="s">
         <v>365</v>
       </c>
-      <c r="M49" s="34" t="s">
+      <c r="M49" s="31" t="s">
         <v>454</v>
       </c>
-      <c r="N49" s="35" t="s">
+      <c r="N49" s="32" t="s">
         <v>263</v>
       </c>
-      <c r="O49" s="35" t="s">
+      <c r="O49" s="32" t="s">
         <v>351</v>
       </c>
     </row>
     <row r="50" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J50" s="34" t="s">
+      <c r="J50" s="31" t="s">
         <v>254</v>
       </c>
-      <c r="K50" s="40" t="s">
+      <c r="K50" s="35" t="s">
         <v>366</v>
       </c>
-      <c r="M50" s="34" t="s">
+      <c r="M50" s="31" t="s">
         <v>455</v>
       </c>
-      <c r="N50" s="35" t="s">
+      <c r="N50" s="32" t="s">
         <v>264</v>
       </c>
-      <c r="O50" s="35" t="s">
+      <c r="O50" s="32" t="s">
         <v>348</v>
       </c>
-      <c r="Q50" s="71" t="s">
+      <c r="Q50" s="63" t="s">
         <v>420</v>
       </c>
-      <c r="R50" s="71"/>
-      <c r="S50" s="71"/>
-      <c r="U50" s="41" t="s">
+      <c r="R50" s="63"/>
+      <c r="S50" s="63"/>
+      <c r="U50" s="67" t="s">
         <v>271</v>
       </c>
-      <c r="V50" s="41"/>
-      <c r="W50" s="41"/>
+      <c r="V50" s="67"/>
+      <c r="W50" s="67"/>
     </row>
     <row r="51" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="53" t="s">
+      <c r="B51" s="71" t="s">
         <v>370</v>
       </c>
-      <c r="C51" s="53"/>
-      <c r="D51" s="53"/>
-      <c r="E51" s="53"/>
-      <c r="G51" s="69" t="s">
+      <c r="C51" s="71"/>
+      <c r="D51" s="71"/>
+      <c r="E51" s="71"/>
+      <c r="G51" s="70" t="s">
         <v>414</v>
       </c>
-      <c r="H51" s="69"/>
-      <c r="J51" s="34" t="s">
+      <c r="H51" s="70"/>
+      <c r="J51" s="31" t="s">
         <v>255</v>
       </c>
-      <c r="K51" s="40" t="s">
+      <c r="K51" s="35" t="s">
         <v>367</v>
       </c>
-      <c r="M51" s="34" t="s">
+      <c r="M51" s="31" t="s">
         <v>456</v>
       </c>
-      <c r="N51" s="35" t="s">
+      <c r="N51" s="32" t="s">
         <v>264</v>
       </c>
-      <c r="O51" s="35" t="s">
+      <c r="O51" s="32" t="s">
         <v>346</v>
       </c>
-      <c r="Q51" s="34" t="s">
+      <c r="Q51" s="31" t="s">
         <v>467</v>
       </c>
-      <c r="R51" s="34" t="s">
+      <c r="R51" s="31" t="s">
         <v>468</v>
       </c>
-      <c r="S51" s="34" t="s">
+      <c r="S51" s="31" t="s">
         <v>469</v>
       </c>
-      <c r="U51" s="34" t="s">
+      <c r="U51" s="31" t="s">
         <v>272</v>
       </c>
-      <c r="V51" s="34" t="s">
+      <c r="V51" s="31" t="s">
         <v>431</v>
       </c>
-      <c r="W51" s="34" t="s">
+      <c r="W51" s="31" t="s">
         <v>430</v>
       </c>
     </row>
     <row r="52" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="34" t="s">
+      <c r="B52" s="31" t="s">
         <v>428</v>
       </c>
-      <c r="C52" s="34" t="s">
+      <c r="C52" s="31" t="s">
         <v>234</v>
       </c>
-      <c r="D52" s="34" t="s">
+      <c r="D52" s="31" t="s">
         <v>372</v>
       </c>
-      <c r="E52" s="34" t="s">
+      <c r="E52" s="31" t="s">
         <v>393</v>
       </c>
-      <c r="G52" s="52" t="s">
+      <c r="G52" s="43" t="s">
         <v>428</v>
       </c>
-      <c r="H52" s="52" t="s">
+      <c r="H52" s="43" t="s">
         <v>415</v>
       </c>
-      <c r="J52" s="34" t="s">
+      <c r="J52" s="31" t="s">
         <v>256</v>
       </c>
-      <c r="K52" s="40" t="s">
+      <c r="K52" s="35" t="s">
         <v>368</v>
       </c>
-      <c r="M52" s="34" t="s">
+      <c r="M52" s="31" t="s">
         <v>457</v>
       </c>
-      <c r="N52" s="35" t="s">
+      <c r="N52" s="32" t="s">
         <v>265</v>
       </c>
-      <c r="O52" s="35" t="s">
+      <c r="O52" s="32" t="s">
         <v>350</v>
       </c>
-      <c r="Q52" s="34" t="s">
+      <c r="Q52" s="31" t="s">
         <v>421</v>
       </c>
-      <c r="R52" s="43" t="s">
+      <c r="R52" s="37" t="s">
         <v>206</v>
       </c>
-      <c r="S52" s="43" t="s">
+      <c r="S52" s="37" t="s">
         <v>207</v>
       </c>
-      <c r="U52" s="42" t="s">
+      <c r="U52" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="V52" s="43" t="s">
+      <c r="V52" s="37" t="s">
         <v>165</v>
       </c>
-      <c r="W52" s="43" t="s">
+      <c r="W52" s="37" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="53" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="34" t="s">
+      <c r="B53" s="31" t="s">
         <v>394</v>
       </c>
-      <c r="C53" s="34" t="s">
+      <c r="C53" s="31" t="s">
         <v>251</v>
       </c>
-      <c r="D53" s="42" t="s">
+      <c r="D53" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="E53" s="35" t="s">
+      <c r="E53" s="32" t="s">
         <v>373</v>
       </c>
-      <c r="G53" s="35" t="s">
+      <c r="G53" s="32" t="s">
         <v>394</v>
       </c>
-      <c r="H53" s="35" t="s">
+      <c r="H53" s="32" t="s">
         <v>251</v>
       </c>
-      <c r="J53" s="34" t="s">
+      <c r="J53" s="31" t="s">
         <v>257</v>
       </c>
-      <c r="K53" s="40" t="s">
+      <c r="K53" s="35" t="s">
         <v>369</v>
       </c>
-      <c r="M53" s="34" t="s">
+      <c r="M53" s="31" t="s">
         <v>458</v>
       </c>
-      <c r="N53" s="35" t="s">
+      <c r="N53" s="32" t="s">
         <v>266</v>
       </c>
-      <c r="O53" s="35" t="s">
+      <c r="O53" s="32" t="s">
         <v>347</v>
       </c>
-      <c r="Q53" s="34" t="s">
+      <c r="Q53" s="31" t="s">
         <v>422</v>
       </c>
-      <c r="R53" s="43" t="s">
+      <c r="R53" s="37" t="s">
         <v>208</v>
       </c>
-      <c r="S53" s="43" t="s">
+      <c r="S53" s="37" t="s">
         <v>209</v>
       </c>
-      <c r="U53" s="44" t="s">
+      <c r="U53" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="V53" s="45" t="s">
+      <c r="V53" s="39" t="s">
         <v>167</v>
       </c>
-      <c r="W53" s="45" t="s">
+      <c r="W53" s="39" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="54" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="34" t="s">
+      <c r="B54" s="31" t="s">
         <v>395</v>
       </c>
-      <c r="C54" s="34" t="s">
+      <c r="C54" s="31" t="s">
         <v>252</v>
       </c>
-      <c r="D54" s="44" t="s">
+      <c r="D54" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="E54" s="35" t="s">
+      <c r="E54" s="32" t="s">
         <v>374</v>
       </c>
-      <c r="G54" s="35" t="s">
+      <c r="G54" s="32" t="s">
         <v>394</v>
       </c>
-      <c r="H54" s="35" t="s">
+      <c r="H54" s="32" t="s">
         <v>252</v>
       </c>
-      <c r="J54" s="34" t="s">
+      <c r="J54" s="31" t="s">
         <v>258</v>
       </c>
-      <c r="K54" s="40" t="s">
+      <c r="K54" s="35" t="s">
         <v>356</v>
       </c>
-      <c r="M54" s="34" t="s">
+      <c r="M54" s="31" t="s">
         <v>459</v>
       </c>
-      <c r="N54" s="35" t="s">
+      <c r="N54" s="32" t="s">
         <v>266</v>
       </c>
-      <c r="O54" s="35" t="s">
+      <c r="O54" s="32" t="s">
         <v>349</v>
       </c>
-      <c r="Q54" s="34" t="s">
+      <c r="Q54" s="31" t="s">
         <v>423</v>
       </c>
-      <c r="R54" s="45" t="s">
+      <c r="R54" s="39" t="s">
         <v>210</v>
       </c>
-      <c r="S54" s="45" t="s">
+      <c r="S54" s="39" t="s">
         <v>182</v>
       </c>
-      <c r="U54" s="44" t="s">
+      <c r="U54" s="38" t="s">
         <v>42</v>
       </c>
-      <c r="V54" s="45" t="s">
+      <c r="V54" s="39" t="s">
         <v>203</v>
       </c>
-      <c r="W54" s="45" t="s">
+      <c r="W54" s="39" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="55" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="34" t="s">
+      <c r="B55" s="31" t="s">
         <v>396</v>
       </c>
-      <c r="C55" s="34" t="s">
+      <c r="C55" s="31" t="s">
         <v>253</v>
       </c>
-      <c r="D55" s="42" t="s">
+      <c r="D55" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="E55" s="35" t="s">
+      <c r="E55" s="32" t="s">
         <v>375</v>
       </c>
-      <c r="G55" s="35" t="s">
+      <c r="G55" s="32" t="s">
         <v>395</v>
       </c>
-      <c r="H55" s="35" t="s">
+      <c r="H55" s="32" t="s">
         <v>253</v>
       </c>
-      <c r="J55" s="34" t="s">
+      <c r="J55" s="31" t="s">
         <v>259</v>
       </c>
-      <c r="K55" s="40" t="s">
+      <c r="K55" s="35" t="s">
         <v>357</v>
       </c>
-      <c r="M55" s="34" t="s">
+      <c r="M55" s="31" t="s">
         <v>460</v>
       </c>
-      <c r="N55" s="35" t="s">
+      <c r="N55" s="32" t="s">
         <v>267</v>
       </c>
-      <c r="O55" s="35" t="s">
+      <c r="O55" s="32" t="s">
         <v>346</v>
       </c>
-      <c r="U55" s="44" t="s">
+      <c r="U55" s="38" t="s">
         <v>57</v>
       </c>
-      <c r="V55" s="45" t="s">
+      <c r="V55" s="39" t="s">
         <v>204</v>
       </c>
-      <c r="W55" s="45" t="s">
+      <c r="W55" s="39" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="56" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="34" t="s">
+      <c r="B56" s="31" t="s">
         <v>397</v>
       </c>
-      <c r="C56" s="34" t="s">
+      <c r="C56" s="31" t="s">
         <v>254</v>
       </c>
-      <c r="D56" s="44" t="s">
+      <c r="D56" s="38" t="s">
         <v>42</v>
       </c>
-      <c r="E56" s="35" t="s">
+      <c r="E56" s="32" t="s">
         <v>376</v>
       </c>
-      <c r="G56" s="35" t="s">
+      <c r="G56" s="32" t="s">
         <v>396</v>
       </c>
-      <c r="H56" s="35" t="s">
+      <c r="H56" s="32" t="s">
         <v>254</v>
       </c>
-      <c r="J56" s="34" t="s">
+      <c r="J56" s="31" t="s">
         <v>260</v>
       </c>
-      <c r="K56" s="40" t="s">
+      <c r="K56" s="35" t="s">
         <v>358</v>
       </c>
-      <c r="M56" s="34" t="s">
+      <c r="M56" s="31" t="s">
         <v>461</v>
       </c>
-      <c r="N56" s="35" t="s">
+      <c r="N56" s="32" t="s">
         <v>267</v>
       </c>
-      <c r="O56" s="35" t="s">
+      <c r="O56" s="32" t="s">
         <v>352</v>
       </c>
     </row>
     <row r="57" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="34" t="s">
+      <c r="B57" s="31" t="s">
         <v>398</v>
       </c>
-      <c r="C57" s="34" t="s">
+      <c r="C57" s="31" t="s">
         <v>255</v>
       </c>
-      <c r="D57" s="42" t="s">
+      <c r="D57" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="E57" s="35" t="s">
+      <c r="E57" s="32" t="s">
         <v>377</v>
       </c>
-      <c r="G57" s="35" t="s">
+      <c r="G57" s="32" t="s">
         <v>397</v>
       </c>
-      <c r="H57" s="35" t="s">
+      <c r="H57" s="32" t="s">
         <v>256</v>
       </c>
-      <c r="J57" s="34" t="s">
+      <c r="J57" s="31" t="s">
         <v>261</v>
       </c>
-      <c r="K57" s="40" t="s">
+      <c r="K57" s="35" t="s">
         <v>359</v>
       </c>
-      <c r="M57" s="34" t="s">
+      <c r="M57" s="31" t="s">
         <v>462</v>
       </c>
-      <c r="N57" s="35" t="s">
+      <c r="N57" s="32" t="s">
         <v>268</v>
       </c>
-      <c r="O57" s="35" t="s">
+      <c r="O57" s="32" t="s">
         <v>351</v>
       </c>
     </row>
     <row r="58" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="34" t="s">
+      <c r="B58" s="31" t="s">
         <v>399</v>
       </c>
-      <c r="C58" s="34" t="s">
+      <c r="C58" s="31" t="s">
         <v>256</v>
       </c>
-      <c r="D58" s="44" t="s">
+      <c r="D58" s="38" t="s">
         <v>57</v>
       </c>
-      <c r="E58" s="35" t="s">
+      <c r="E58" s="32" t="s">
         <v>378</v>
       </c>
-      <c r="G58" s="35" t="s">
+      <c r="G58" s="32" t="s">
         <v>397</v>
       </c>
-      <c r="H58" s="35" t="s">
+      <c r="H58" s="32" t="s">
         <v>258</v>
       </c>
-      <c r="J58" s="34" t="s">
+      <c r="J58" s="31" t="s">
         <v>262</v>
       </c>
-      <c r="K58" s="40" t="s">
+      <c r="K58" s="35" t="s">
         <v>360</v>
       </c>
-      <c r="M58" s="34" t="s">
+      <c r="M58" s="31" t="s">
         <v>463</v>
       </c>
-      <c r="N58" s="35" t="s">
+      <c r="N58" s="32" t="s">
         <v>269</v>
       </c>
-      <c r="O58" s="35" t="s">
+      <c r="O58" s="32" t="s">
         <v>348</v>
       </c>
     </row>
     <row r="59" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="34" t="s">
+      <c r="B59" s="31" t="s">
         <v>400</v>
       </c>
-      <c r="C59" s="34" t="s">
+      <c r="C59" s="31" t="s">
         <v>257</v>
       </c>
-      <c r="D59" s="42" t="s">
+      <c r="D59" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="E59" s="35" t="s">
+      <c r="E59" s="32" t="s">
         <v>379</v>
       </c>
-      <c r="G59" s="35" t="s">
+      <c r="G59" s="32" t="s">
         <v>398</v>
       </c>
-      <c r="H59" s="35" t="s">
+      <c r="H59" s="32" t="s">
         <v>257</v>
       </c>
-      <c r="J59" s="34" t="s">
+      <c r="J59" s="31" t="s">
         <v>263</v>
       </c>
-      <c r="K59" s="40" t="s">
+      <c r="K59" s="35" t="s">
         <v>361</v>
       </c>
-      <c r="M59" s="34" t="s">
+      <c r="M59" s="31" t="s">
         <v>464</v>
       </c>
-      <c r="N59" s="35" t="s">
+      <c r="N59" s="32" t="s">
         <v>269</v>
       </c>
-      <c r="O59" s="35" t="s">
+      <c r="O59" s="32" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="60" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="34" t="s">
+      <c r="B60" s="31" t="s">
         <v>401</v>
       </c>
-      <c r="C60" s="34" t="s">
+      <c r="C60" s="31" t="s">
         <v>258</v>
       </c>
-      <c r="D60" s="44" t="s">
+      <c r="D60" s="38" t="s">
         <v>42</v>
       </c>
-      <c r="E60" s="35" t="s">
+      <c r="E60" s="32" t="s">
         <v>380</v>
       </c>
-      <c r="G60" s="35" t="s">
+      <c r="G60" s="32" t="s">
         <v>399</v>
       </c>
-      <c r="H60" s="35" t="s">
+      <c r="H60" s="32" t="s">
         <v>260</v>
       </c>
-      <c r="J60" s="34" t="s">
+      <c r="J60" s="31" t="s">
         <v>264</v>
       </c>
-      <c r="K60" s="40" t="s">
+      <c r="K60" s="35" t="s">
         <v>362</v>
       </c>
-      <c r="M60" s="34" t="s">
+      <c r="M60" s="31" t="s">
         <v>465</v>
       </c>
-      <c r="N60" s="35" t="s">
+      <c r="N60" s="32" t="s">
         <v>270</v>
       </c>
-      <c r="O60" s="35" t="s">
+      <c r="O60" s="32" t="s">
         <v>349</v>
       </c>
     </row>
     <row r="61" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="34" t="s">
+      <c r="B61" s="31" t="s">
         <v>402</v>
       </c>
-      <c r="C61" s="34" t="s">
+      <c r="C61" s="31" t="s">
         <v>259</v>
       </c>
-      <c r="D61" s="42" t="s">
+      <c r="D61" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="E61" s="35" t="s">
+      <c r="E61" s="32" t="s">
         <v>381</v>
       </c>
-      <c r="G61" s="35" t="s">
+      <c r="G61" s="32" t="s">
         <v>399</v>
       </c>
-      <c r="H61" s="35" t="s">
+      <c r="H61" s="32" t="s">
         <v>251</v>
       </c>
-      <c r="M61" s="34" t="s">
+      <c r="M61" s="31" t="s">
         <v>466</v>
       </c>
-      <c r="N61" s="35" t="s">
+      <c r="N61" s="32" t="s">
         <v>270</v>
       </c>
-      <c r="O61" s="35" t="s">
+      <c r="O61" s="32" t="s">
         <v>346</v>
       </c>
     </row>
     <row r="62" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="34" t="s">
+      <c r="B62" s="31" t="s">
         <v>403</v>
       </c>
-      <c r="C62" s="34" t="s">
+      <c r="C62" s="31" t="s">
         <v>260</v>
       </c>
-      <c r="D62" s="44" t="s">
+      <c r="D62" s="38" t="s">
         <v>57</v>
       </c>
-      <c r="E62" s="35" t="s">
+      <c r="E62" s="32" t="s">
         <v>382</v>
       </c>
-      <c r="G62" s="35" t="s">
+      <c r="G62" s="32" t="s">
         <v>400</v>
       </c>
-      <c r="H62" s="35" t="s">
+      <c r="H62" s="32" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="63" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B63" s="34" t="s">
+      <c r="B63" s="31" t="s">
         <v>404</v>
       </c>
-      <c r="C63" s="34" t="s">
+      <c r="C63" s="31" t="s">
         <v>261</v>
       </c>
-      <c r="D63" s="42" t="s">
+      <c r="D63" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="E63" s="35" t="s">
+      <c r="E63" s="32" t="s">
         <v>383</v>
       </c>
-      <c r="G63" s="35" t="s">
+      <c r="G63" s="32" t="s">
         <v>400</v>
       </c>
-      <c r="H63" s="35" t="s">
+      <c r="H63" s="32" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="64" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B64" s="34" t="s">
+      <c r="B64" s="31" t="s">
         <v>405</v>
       </c>
-      <c r="C64" s="34" t="s">
+      <c r="C64" s="31" t="s">
         <v>262</v>
       </c>
-      <c r="D64" s="44" t="s">
+      <c r="D64" s="38" t="s">
         <v>42</v>
       </c>
-      <c r="E64" s="35" t="s">
+      <c r="E64" s="32" t="s">
         <v>384</v>
       </c>
-      <c r="G64" s="35" t="s">
+      <c r="G64" s="32" t="s">
         <v>401</v>
       </c>
-      <c r="H64" s="35" t="s">
+      <c r="H64" s="32" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="65" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B65" s="34" t="s">
+      <c r="B65" s="31" t="s">
         <v>406</v>
       </c>
-      <c r="C65" s="34" t="s">
+      <c r="C65" s="31" t="s">
         <v>263</v>
       </c>
-      <c r="D65" s="42" t="s">
+      <c r="D65" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="E65" s="35" t="s">
+      <c r="E65" s="32" t="s">
         <v>385</v>
       </c>
-      <c r="G65" s="35" t="s">
+      <c r="G65" s="32" t="s">
         <v>402</v>
       </c>
-      <c r="H65" s="35" t="s">
+      <c r="H65" s="32" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="66" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B66" s="34" t="s">
+      <c r="B66" s="31" t="s">
         <v>407</v>
       </c>
-      <c r="C66" s="34" t="s">
+      <c r="C66" s="31" t="s">
         <v>264</v>
       </c>
-      <c r="D66" s="44" t="s">
+      <c r="D66" s="38" t="s">
         <v>57</v>
       </c>
-      <c r="E66" s="35" t="s">
+      <c r="E66" s="32" t="s">
         <v>386</v>
       </c>
-      <c r="G66" s="35" t="s">
+      <c r="G66" s="32" t="s">
         <v>402</v>
       </c>
-      <c r="H66" s="35" t="s">
+      <c r="H66" s="32" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="67" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="34" t="s">
+      <c r="B67" s="31" t="s">
         <v>408</v>
       </c>
-      <c r="C67" s="34" t="s">
+      <c r="C67" s="31" t="s">
         <v>265</v>
       </c>
-      <c r="D67" s="42" t="s">
+      <c r="D67" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="E67" s="35" t="s">
+      <c r="E67" s="32" t="s">
         <v>387</v>
       </c>
-      <c r="G67" s="35" t="s">
+      <c r="G67" s="32" t="s">
         <v>403</v>
       </c>
-      <c r="H67" s="35" t="s">
+      <c r="H67" s="32" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="68" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B68" s="34" t="s">
+      <c r="B68" s="31" t="s">
         <v>409</v>
       </c>
-      <c r="C68" s="34" t="s">
+      <c r="C68" s="31" t="s">
         <v>266</v>
       </c>
-      <c r="D68" s="44" t="s">
+      <c r="D68" s="38" t="s">
         <v>42</v>
       </c>
-      <c r="E68" s="35" t="s">
+      <c r="E68" s="32" t="s">
         <v>388</v>
       </c>
-      <c r="G68" s="35" t="s">
+      <c r="G68" s="32" t="s">
         <v>404</v>
       </c>
-      <c r="H68" s="35" t="s">
+      <c r="H68" s="32" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="69" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="34" t="s">
+      <c r="B69" s="31" t="s">
         <v>410</v>
       </c>
-      <c r="C69" s="34" t="s">
+      <c r="C69" s="31" t="s">
         <v>267</v>
       </c>
-      <c r="D69" s="42" t="s">
+      <c r="D69" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="E69" s="35" t="s">
+      <c r="E69" s="32" t="s">
         <v>389</v>
       </c>
-      <c r="G69" s="35" t="s">
+      <c r="G69" s="32" t="s">
         <v>404</v>
       </c>
-      <c r="H69" s="35" t="s">
+      <c r="H69" s="32" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="70" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B70" s="34" t="s">
+      <c r="B70" s="31" t="s">
         <v>411</v>
       </c>
-      <c r="C70" s="34" t="s">
+      <c r="C70" s="31" t="s">
         <v>268</v>
       </c>
-      <c r="D70" s="44" t="s">
+      <c r="D70" s="38" t="s">
         <v>57</v>
       </c>
-      <c r="E70" s="35" t="s">
+      <c r="E70" s="32" t="s">
         <v>390</v>
       </c>
-      <c r="G70" s="35" t="s">
+      <c r="G70" s="32" t="s">
         <v>405</v>
       </c>
-      <c r="H70" s="35" t="s">
+      <c r="H70" s="32" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="71" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B71" s="34" t="s">
+      <c r="B71" s="31" t="s">
         <v>412</v>
       </c>
-      <c r="C71" s="34" t="s">
+      <c r="C71" s="31" t="s">
         <v>269</v>
       </c>
-      <c r="D71" s="42" t="s">
+      <c r="D71" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="E71" s="35" t="s">
+      <c r="E71" s="32" t="s">
         <v>391</v>
       </c>
-      <c r="G71" s="35" t="s">
+      <c r="G71" s="32" t="s">
         <v>406</v>
       </c>
-      <c r="H71" s="35" t="s">
+      <c r="H71" s="32" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="72" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B72" s="34" t="s">
+      <c r="B72" s="31" t="s">
         <v>413</v>
       </c>
-      <c r="C72" s="34" t="s">
+      <c r="C72" s="31" t="s">
         <v>270</v>
       </c>
-      <c r="D72" s="44" t="s">
+      <c r="D72" s="38" t="s">
         <v>42</v>
       </c>
-      <c r="E72" s="35" t="s">
+      <c r="E72" s="32" t="s">
         <v>392</v>
       </c>
-      <c r="G72" s="35" t="s">
+      <c r="G72" s="32" t="s">
         <v>406</v>
       </c>
-      <c r="H72" s="35" t="s">
+      <c r="H72" s="32" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="73" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G73" s="35" t="s">
+      <c r="G73" s="32" t="s">
         <v>407</v>
       </c>
-      <c r="H73" s="35" t="s">
+      <c r="H73" s="32" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="74" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G74" s="35" t="s">
+      <c r="G74" s="32" t="s">
         <v>407</v>
       </c>
-      <c r="H74" s="35" t="s">
+      <c r="H74" s="32" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="75" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G75" s="35" t="s">
+      <c r="G75" s="32" t="s">
         <v>408</v>
       </c>
-      <c r="H75" s="35" t="s">
+      <c r="H75" s="32" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="76" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G76" s="35" t="s">
+      <c r="G76" s="32" t="s">
         <v>409</v>
       </c>
-      <c r="H76" s="35" t="s">
+      <c r="H76" s="32" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="77" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G77" s="35" t="s">
+      <c r="G77" s="32" t="s">
         <v>409</v>
       </c>
-      <c r="H77" s="35" t="s">
+      <c r="H77" s="32" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="78" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G78" s="35" t="s">
+      <c r="G78" s="32" t="s">
         <v>410</v>
       </c>
-      <c r="H78" s="35" t="s">
+      <c r="H78" s="32" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="79" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G79" s="35" t="s">
+      <c r="G79" s="32" t="s">
         <v>410</v>
       </c>
-      <c r="H79" s="35" t="s">
+      <c r="H79" s="32" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="80" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G80" s="35" t="s">
+      <c r="G80" s="32" t="s">
         <v>411</v>
       </c>
-      <c r="H80" s="35" t="s">
+      <c r="H80" s="32" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="81" spans="5:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G81" s="35" t="s">
+      <c r="G81" s="32" t="s">
         <v>412</v>
       </c>
-      <c r="H81" s="35" t="s">
+      <c r="H81" s="32" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="82" spans="5:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G82" s="35" t="s">
+      <c r="G82" s="32" t="s">
         <v>412</v>
       </c>
-      <c r="H82" s="35" t="s">
+      <c r="H82" s="32" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="83" spans="5:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G83" s="35" t="s">
+      <c r="G83" s="32" t="s">
         <v>413</v>
       </c>
-      <c r="H83" s="35" t="s">
+      <c r="H83" s="32" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="84" spans="5:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G84" s="35" t="s">
+      <c r="G84" s="32" t="s">
         <v>413</v>
       </c>
-      <c r="H84" s="35" t="s">
+      <c r="H84" s="32" t="s">
         <v>251</v>
       </c>
     </row>
@@ -11096,6 +11096,9 @@
     <row r="98" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="G51:H51"/>
+    <mergeCell ref="B51:E51"/>
+    <mergeCell ref="M26:O26"/>
     <mergeCell ref="Q50:S50"/>
     <mergeCell ref="T26:W26"/>
     <mergeCell ref="B26:H26"/>
@@ -11104,9 +11107,6 @@
     <mergeCell ref="U50:W50"/>
     <mergeCell ref="J34:K34"/>
     <mergeCell ref="J45:K45"/>
-    <mergeCell ref="G51:H51"/>
-    <mergeCell ref="B51:E51"/>
-    <mergeCell ref="M26:O26"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11125,13 +11125,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="75" t="s">
         <v>140</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
     </row>
     <row r="3" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
